--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -62886,6 +62886,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>16700</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -62932,6 +62932,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>2260</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.716000020503998</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -62796,10 +62796,10 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>19121</v>
+        <v>1850</v>
       </c>
       <c r="C2715" t="n">
         <v>0.716000020503998</v>
@@ -62819,19 +62819,19 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>0</v>
+        <v>19121</v>
       </c>
       <c r="C2716" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.716000020503998</v>
+        <v>0.708000004291534</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.716000020503998</v>
+        <v>0.708000004291534</v>
       </c>
       <c r="F2716" t="n">
         <v>0.716000020503998</v>
@@ -62842,16 +62842,16 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C2717" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.708000004291534</v>
+        <v>0.716000020503998</v>
       </c>
       <c r="E2717" t="n">
         <v>0.716000020503998</v>
@@ -62865,16 +62865,16 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2580</v>
+        <v>102</v>
       </c>
       <c r="C2718" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.716000020503998</v>
+        <v>0.708000004291534</v>
       </c>
       <c r="E2718" t="n">
         <v>0.716000020503998</v>
@@ -62888,10 +62888,10 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>0</v>
+        <v>2580</v>
       </c>
       <c r="C2719" t="n">
         <v>0.716000020503998</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="C2720" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.708000004291534</v>
+        <v>0.716000020503998</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.708000004291534</v>
+        <v>0.716000020503998</v>
       </c>
       <c r="F2720" t="n">
         <v>0.716000020503998</v>
@@ -62934,19 +62934,19 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="C2721" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.716000020503998</v>
+        <v>0.708000004291534</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.716000020503998</v>
+        <v>0.708000004291534</v>
       </c>
       <c r="F2721" t="n">
         <v>0.716000020503998</v>
@@ -62957,19 +62957,19 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>2260</v>
+        <v>0</v>
       </c>
       <c r="C2722" t="n">
         <v>0.716000020503998</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.709999978542328</v>
+        <v>0.716000020503998</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.709999978542328</v>
+        <v>0.716000020503998</v>
       </c>
       <c r="F2722" t="n">
         <v>0.716000020503998</v>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63047,6 +63047,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="G2726" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63155,7 +63155,9 @@
       <c r="E2730" t="n">
         <v>0.736000001430511</v>
       </c>
-      <c r="F2730"/>
+      <c r="F2730" t="n">
+        <v>0.740000009536743</v>
+      </c>
       <c r="G2730" t="s">
         <v>7</v>
       </c>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.765999972820282</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.75</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>19184</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.726000010967255</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.75</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.745999991893768</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>444</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.730000019073486</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.730000019073486</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>7103</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.723999977111816</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.730000019073486</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.730000019073486</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>27600</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -941,7 +941,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G22" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G23" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G24" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G25" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G26" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G27" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G28" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G29" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G30" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G31" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G32" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G33" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G34" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G35" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G36" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G37" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G38" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G39" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899916529655</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.24974599480629</v>
       </c>
       <c r="G40" t="n">
-        <v>0.210174262523651</v>
+        <v>0.21017424762249</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.24974599480629</v>
       </c>
       <c r="G41" t="n">
-        <v>0.210174262523651</v>
+        <v>0.21017424762249</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.24974599480629</v>
       </c>
       <c r="G42" t="n">
-        <v>0.210174262523651</v>
+        <v>0.21017424762249</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.24974599480629</v>
       </c>
       <c r="G43" t="n">
-        <v>0.210174262523651</v>
+        <v>0.21017424762249</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.24974599480629</v>
       </c>
       <c r="G44" t="n">
-        <v>0.210174262523651</v>
+        <v>0.21017424762249</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.250844985246658</v>
       </c>
       <c r="G45" t="n">
-        <v>0.211099103093147</v>
+        <v>0.211099088191986</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.250844985246658</v>
       </c>
       <c r="G46" t="n">
-        <v>0.211099103093147</v>
+        <v>0.211099088191986</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.264730989933014</v>
       </c>
       <c r="G242" t="n">
-        <v>0.222784891724586</v>
+        <v>0.222784876823425</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.264730989933014</v>
       </c>
       <c r="G243" t="n">
-        <v>0.222784891724586</v>
+        <v>0.222784876823425</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.264730989933014</v>
       </c>
       <c r="G244" t="n">
-        <v>0.222784891724586</v>
+        <v>0.222784876823425</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.264730989933014</v>
       </c>
       <c r="G245" t="n">
-        <v>0.222784891724586</v>
+        <v>0.222784876823425</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G246" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G247" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.259736001491547</v>
       </c>
       <c r="G248" t="n">
-        <v>0.218581363558769</v>
+        <v>0.218581348657608</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G251" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G252" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G253" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G254" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G255" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G256" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G257" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G258" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G259" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G260" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G261" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G262" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G263" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G264" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G265" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G266" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G267" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G268" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G269" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G270" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G271" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G272" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G273" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G274" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014971137047</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.234760999679565</v>
       </c>
       <c r="G282" t="n">
-        <v>0.197563603520393</v>
+        <v>0.197563588619232</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.234760999679565</v>
       </c>
       <c r="G283" t="n">
-        <v>0.197563603520393</v>
+        <v>0.197563588619232</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>0.233761996030807</v>
       </c>
       <c r="G287" t="n">
-        <v>0.196722880005836</v>
+        <v>0.196722894906998</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.233761996030807</v>
       </c>
       <c r="G288" t="n">
-        <v>0.196722880005836</v>
+        <v>0.196722894906998</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.233761996030807</v>
       </c>
       <c r="G289" t="n">
-        <v>0.196722880005836</v>
+        <v>0.196722894906998</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>0.243852004408836</v>
       </c>
       <c r="G323" t="n">
-        <v>0.205214127898216</v>
+        <v>0.205214142799377</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>0.243852004408836</v>
       </c>
       <c r="G324" t="n">
-        <v>0.205214127898216</v>
+        <v>0.205214142799377</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.255739986896515</v>
       </c>
       <c r="G327" t="n">
-        <v>0.215218514204025</v>
+        <v>0.215218499302864</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>0.269724994897842</v>
       </c>
       <c r="G331" t="n">
-        <v>0.226987600326538</v>
+        <v>0.226987615227699</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.269724994897842</v>
       </c>
       <c r="G332" t="n">
-        <v>0.226987600326538</v>
+        <v>0.226987615227699</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G349" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G350" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G351" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G352" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G353" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G354" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G355" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G356" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G357" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.286707997322083</v>
       </c>
       <c r="G358" t="n">
-        <v>0.241279661655426</v>
+        <v>0.241279691457748</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G381" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G382" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G383" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G384" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G385" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G386" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093863725662</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G389" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G390" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G391" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G392" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G393" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G394" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G395" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>0.318675994873047</v>
       </c>
       <c r="G396" t="n">
-        <v>0.268182456493378</v>
+        <v>0.268182426691055</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.377315998077393</v>
       </c>
       <c r="G409" t="n">
-        <v>0.317531019449234</v>
+        <v>0.317531049251556</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>0.449542999267578</v>
       </c>
       <c r="G421" t="n">
-        <v>0.378313839435577</v>
+        <v>0.378313809633255</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>0.499491989612579</v>
       </c>
       <c r="G423" t="n">
-        <v>0.420348525047302</v>
+        <v>0.42034849524498</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.523468017578125</v>
       </c>
       <c r="G424" t="n">
-        <v>0.440525591373444</v>
+        <v>0.440525561571121</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G552" t="n">
-        <v>0.492307841777802</v>
+        <v>0.492307871580124</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G553" t="n">
-        <v>0.492307841777802</v>
+        <v>0.492307871580124</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G554" t="n">
-        <v>0.492307841777802</v>
+        <v>0.492307871580124</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G558" t="n">
-        <v>0.715319335460663</v>
+        <v>0.715319275856018</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G572" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G581" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G582" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G583" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G584" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G585" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G586" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G587" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G588" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G589" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.492307841777802</v>
+        <v>0.492307871580124</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G591" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G616" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G617" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G618" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G619" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G620" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G645" t="n">
-        <v>0.492307841777802</v>
+        <v>0.492307871580124</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G646" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G647" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G650" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G653" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G655" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G656" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G662" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G663" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G664" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G686" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G687" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G688" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G689" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G700" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G701" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G702" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G703" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G704" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G723" t="n">
-        <v>0.534385561943054</v>
+        <v>0.534385502338409</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>0.534385561943054</v>
+        <v>0.534385502338409</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G729" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G731" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G732" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G733" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G745" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G768" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G769" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G770" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G771" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G772" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G773" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G774" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G775" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G778" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G789" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G790" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G794" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G798" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G802" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G803" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G824" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G828" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G829" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G830" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G831" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G835" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G836" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G837" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G838" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G841" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G856" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G862" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G887" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G888" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G889" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G891" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G897" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G898" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G900" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G912" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G913" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G914" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G915" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G916" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G917" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G918" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G919" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G921" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G937" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G938" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G940" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G941" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G946" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G947" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G948" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G949" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G950" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G951" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G952" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G961" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G973" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G974" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G975" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G979" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G980" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G983" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G984" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G985" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G986" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G987" t="n">
-        <v>0.395529448986053</v>
+        <v>0.395529419183731</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G990" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G991" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G992" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G993" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.408994257450104</v>
+        <v>0.408994287252426</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.353451818227768</v>
+        <v>0.35345184803009</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.351768732070923</v>
+        <v>0.351768761873245</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.345036327838898</v>
+        <v>0.345036298036575</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.345036327838898</v>
+        <v>0.345036298036575</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.345036327838898</v>
+        <v>0.345036298036575</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.3500856757164</v>
+        <v>0.350085645914078</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.338303923606873</v>
+        <v>0.33830389380455</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.343353241682053</v>
+        <v>0.34335321187973</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.343353241682053</v>
+        <v>0.34335321187973</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.33998703956604</v>
+        <v>0.339987009763718</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.368599772453308</v>
+        <v>0.36859980225563</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.397212594747543</v>
+        <v>0.397212564945221</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.397212594747543</v>
+        <v>0.397212564945221</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.383747756481171</v>
+        <v>0.383747726678848</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.383747756481171</v>
+        <v>0.383747726678848</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698348999023</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.368599772453308</v>
+        <v>0.36859980225563</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.353451818227768</v>
+        <v>0.35345184803009</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.402261823415756</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.407311171293259</v>
+        <v>0.407311201095581</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.417409807443619</v>
+        <v>0.417409777641296</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.429191499948502</v>
+        <v>0.429191529750824</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.433399260044098</v>
+        <v>0.43339928984642</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.551216542720795</v>
+        <v>0.551216602325439</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.462853640317917</v>
+        <v>0.462853610515594</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.483892410993576</v>
+        <v>0.483892351388931</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.479684591293335</v>
+        <v>0.47968465089798</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.476318418979645</v>
+        <v>0.47631847858429</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.49146643280983</v>
+        <v>0.491466373205185</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.526811540126801</v>
+        <v>0.526811480522156</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.488100200891495</v>
+        <v>0.48810014128685</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.501565039157867</v>
+        <v>0.501564979553223</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.501565039157867</v>
+        <v>0.501564979553223</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.501565039157867</v>
+        <v>0.501564979553223</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.509980499744415</v>
+        <v>0.50998055934906</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.515029847621918</v>
+        <v>0.515029907226562</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.560473680496216</v>
+        <v>0.560473620891571</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.526811540126801</v>
+        <v>0.526811480522156</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.560473680496216</v>
+        <v>0.560473620891571</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.538593292236328</v>
+        <v>0.538593351840973</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.526811540126801</v>
+        <v>0.526811480522156</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.530177772045135</v>
+        <v>0.530177712440491</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.515029847621918</v>
+        <v>0.515029907226562</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.526811540126801</v>
+        <v>0.526811480522156</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.526811540126801</v>
+        <v>0.526811480522156</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.53180605173111</v>
+        <v>0.531806111335754</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.535281896591187</v>
+        <v>0.535281956195831</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.526592254638672</v>
+        <v>0.526592314243317</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.53180605173111</v>
+        <v>0.531806111335754</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.53180605173111</v>
+        <v>0.531806111335754</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.53180605173111</v>
+        <v>0.531806111335754</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.547447443008423</v>
+        <v>0.547447383403778</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.547447443008423</v>
+        <v>0.547447383403778</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.543971538543701</v>
+        <v>0.543971478939056</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.543971538543701</v>
+        <v>0.543971478939056</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.543971538543701</v>
+        <v>0.543971478939056</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.543971538543701</v>
+        <v>0.543971478939056</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.543971538543701</v>
+        <v>0.543971478939056</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.535281896591187</v>
+        <v>0.535281956195831</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.535281896591187</v>
+        <v>0.535281956195831</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.547447443008423</v>
+        <v>0.547447383403778</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.502261281013489</v>
+        <v>0.502261221408844</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.50399923324585</v>
+        <v>0.503999173641205</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.491833686828613</v>
+        <v>0.491833746433258</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.526592254638672</v>
+        <v>0.526592314243317</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.587419807910919</v>
+        <v>0.587419748306274</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.587419807910919</v>
+        <v>0.587419748306274</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.639557600021362</v>
+        <v>0.639557659626007</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.669102370738983</v>
+        <v>0.669102311134338</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.669102370738983</v>
+        <v>0.669102311134338</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.627392113208771</v>
+        <v>0.627392053604126</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.622178375720978</v>
+        <v>0.622178316116333</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.610012829303741</v>
+        <v>0.610012888908386</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.535281896591187</v>
+        <v>0.535281956195831</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.557875037193298</v>
+        <v>0.557874977588654</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.596109390258789</v>
+        <v>0.596109449863434</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.611750781536102</v>
+        <v>0.611750841140747</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985253810883</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.636081695556641</v>
+        <v>0.636081755161285</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.636081695556641</v>
+        <v>0.636081755161285</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.689957499504089</v>
+        <v>0.689957559108734</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.689957499504089</v>
+        <v>0.689957559108734</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.662150681018829</v>
+        <v>0.662150621414185</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.669102370738983</v>
+        <v>0.669102311134338</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.669102370738983</v>
+        <v>0.669102311134338</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985253810883</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985253810883</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.658674895763397</v>
+        <v>0.658674836158752</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.646509349346161</v>
+        <v>0.646509408950806</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.646509349346161</v>
+        <v>0.646509408950806</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.646509349346161</v>
+        <v>0.646509408950806</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.60653692483902</v>
+        <v>0.606536984443665</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.611750781536102</v>
+        <v>0.611750841140747</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.622178375720978</v>
+        <v>0.622178316116333</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.636081695556641</v>
+        <v>0.636081755161285</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.64178854227066</v>
+        <v>0.641788482666016</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.64178854227066</v>
+        <v>0.641788482666016</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.629239559173584</v>
+        <v>0.629239618778229</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.614897906780243</v>
+        <v>0.614897966384888</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.596970915794373</v>
+        <v>0.596970856189728</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.64178854227066</v>
+        <v>0.641788482666016</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.58800733089447</v>
+        <v>0.588007390499115</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.596970915794373</v>
+        <v>0.596970856189728</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.573665678501129</v>
+        <v>0.573665738105774</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.55215322971344</v>
+        <v>0.552153289318085</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.629239559173584</v>
+        <v>0.629239618778229</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1685" t="n">
-        <v>0.629239559173584</v>
+        <v>0.629239618778229</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.60593444108963</v>
+        <v>0.605934381484985</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.60593444108963</v>
+        <v>0.605934381484985</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.60593444108963</v>
+        <v>0.605934381484985</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.58800733089447</v>
+        <v>0.588007390499115</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.548567831516266</v>
+        <v>0.548567891120911</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.564702212810516</v>
+        <v>0.564702153205872</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.548567831516266</v>
+        <v>0.548567891120911</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.573665678501129</v>
+        <v>0.573665738105774</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.573665678501129</v>
+        <v>0.573665738105774</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.60593444108963</v>
+        <v>0.605934381484985</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.60593444108963</v>
+        <v>0.605934381484985</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.596970915794373</v>
+        <v>0.596970856189728</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.614897906780243</v>
+        <v>0.614897966384888</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.614897906780243</v>
+        <v>0.614897966384888</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.62565416097641</v>
+        <v>0.625654220581055</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.638203144073486</v>
+        <v>0.638203084468842</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.638203144073486</v>
+        <v>0.638203084468842</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.638203144073486</v>
+        <v>0.638203084468842</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.629239559173584</v>
+        <v>0.629239618778229</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.666886389255524</v>
+        <v>0.666886448860168</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.647166669368744</v>
+        <v>0.647166609764099</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.666886389255524</v>
+        <v>0.666886448860168</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.670471787452698</v>
+        <v>0.670471847057343</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.683020770549774</v>
+        <v>0.683020710945129</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.690191626548767</v>
+        <v>0.690191566944122</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.715289413928986</v>
+        <v>0.71528947353363</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.743972718715668</v>
+        <v>0.743972778320312</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.711704015731812</v>
+        <v>0.711704075336456</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.735009253025055</v>
+        <v>0.73500919342041</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.735009253025055</v>
+        <v>0.73500919342041</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.745765507221222</v>
+        <v>0.745765447616577</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.745765507221222</v>
+        <v>0.745765447616577</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.743972718715668</v>
+        <v>0.743972778320312</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.708118617534637</v>
+        <v>0.708118677139282</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.690191626548767</v>
+        <v>0.690191566944122</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.700947761535645</v>
+        <v>0.700947821140289</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.69736236333847</v>
+        <v>0.697362422943115</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.724252998828888</v>
+        <v>0.724252939224243</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.711704015731812</v>
+        <v>0.711704075336456</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.708118617534637</v>
+        <v>0.708118677139282</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.683020770549774</v>
+        <v>0.683020710945129</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.690191626548767</v>
+        <v>0.690191566944122</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.690191626548767</v>
+        <v>0.690191566944122</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.690191626548767</v>
+        <v>0.690191566944122</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.720667600631714</v>
+        <v>0.720667541027069</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.724252998828888</v>
+        <v>0.724252939224243</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.715289413928986</v>
+        <v>0.71528947353363</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.724252998828888</v>
+        <v>0.724252939224243</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.724252998828888</v>
+        <v>0.724252939224243</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.711704015731812</v>
+        <v>0.711704075336456</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.724252998828888</v>
+        <v>0.724252939224243</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.708118617534637</v>
+        <v>0.708118677139282</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.683020770549774</v>
+        <v>0.683020710945129</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.631032288074493</v>
+        <v>0.631032347679138</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.659898459911346</v>
+        <v>0.659898400306702</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.659898459911346</v>
+        <v>0.659898400306702</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.663605749607086</v>
+        <v>0.663605690002441</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.659898459911346</v>
+        <v>0.659898400306702</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.659898459911346</v>
+        <v>0.659898400306702</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.659898459911346</v>
+        <v>0.659898400306702</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.583898901939392</v>
+        <v>0.583898842334747</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="n">
-        <v>0.604288995265961</v>
+        <v>0.604289054870605</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="n">
-        <v>0.593167066574097</v>
+        <v>0.593167126178741</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="n">
-        <v>0.595020830631256</v>
+        <v>0.595020771026611</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.54126501083374</v>
+        <v>0.541264951229095</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.583898901939392</v>
+        <v>0.583898842334747</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.593167066574097</v>
+        <v>0.593167126178741</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="n">
-        <v>0.570923328399658</v>
+        <v>0.570923388004303</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.583898901939392</v>
+        <v>0.583898842334747</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.617264568805695</v>
+        <v>0.61726450920105</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.617264568805695</v>
+        <v>0.61726450920105</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.617264568805695</v>
+        <v>0.61726450920105</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="n">
-        <v>0.593167066574097</v>
+        <v>0.593167126178741</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.604288995265961</v>
+        <v>0.604289054870605</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.604288995265961</v>
+        <v>0.604289054870605</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="n">
-        <v>0.617264568805695</v>
+        <v>0.61726450920105</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.652483820915222</v>
+        <v>0.652483880519867</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="n">
-        <v>0.626532793045044</v>
+        <v>0.626532733440399</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="n">
-        <v>0.635800957679749</v>
+        <v>0.635801017284393</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="n">
-        <v>0.646922886371613</v>
+        <v>0.646922945976257</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -56633,7 +56633,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="n">
-        <v>0.650630176067352</v>
+        <v>0.650630235671997</v>
       </c>
       <c r="H2164" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.759999990463257</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>448</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -572,7 +572,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H7" t="n">
         <v>9139</v>
@@ -601,7 +601,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H8" t="n">
         <v>6006</v>
@@ -630,7 +630,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G9" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G11" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G12" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G13" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H13" t="n">
         <v>9880</v>
@@ -775,7 +775,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G14" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G15" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G16" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G17" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G18" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G20" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G21" t="n">
-        <v>0.228249102830887</v>
+        <v>0.228249132633209</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G73" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H73" t="n">
         <v>159</v>
@@ -2515,7 +2515,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G74" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G75" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G76" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G77" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G78" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G79" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G80" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G81" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G82" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G83" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G84" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G85" t="n">
-        <v>0.233293369412422</v>
+        <v>0.233293354511261</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G151" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H151" t="n">
         <v>11211</v>
@@ -4777,7 +4777,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G152" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G153" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G154" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G155" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G156" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G157" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G158" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G159" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G160" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G161" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G162" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G163" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G164" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G165" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G166" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G167" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G168" t="n">
-        <v>0.229762211441994</v>
+        <v>0.229762196540833</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G205" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H205" t="n">
         <v>1</v>
@@ -6343,7 +6343,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G206" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G207" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G208" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G209" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G210" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G211" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G212" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G213" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G214" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G215" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G216" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G217" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G218" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0.279615014791489</v>
       </c>
       <c r="G219" t="n">
-        <v>0.235310569405556</v>
+        <v>0.235310599207878</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0.264829993247986</v>
       </c>
       <c r="G241" t="n">
-        <v>0.222868219017982</v>
+        <v>0.222868204116821</v>
       </c>
       <c r="H241" t="n">
         <v>996</v>
@@ -8344,7 +8344,7 @@
         <v>0.244751006364822</v>
       </c>
       <c r="G275" t="n">
-        <v>0.20597068965435</v>
+        <v>0.205970704555511</v>
       </c>
       <c r="H275" t="n">
         <v>2502</v>
@@ -8373,7 +8373,7 @@
         <v>0.244751006364822</v>
       </c>
       <c r="G276" t="n">
-        <v>0.20597068965435</v>
+        <v>0.205970704555511</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>0.244751006364822</v>
       </c>
       <c r="G277" t="n">
-        <v>0.20597068965435</v>
+        <v>0.205970704555511</v>
       </c>
       <c r="H277" t="n">
         <v>1764</v>
@@ -8431,7 +8431,7 @@
         <v>0.244751006364822</v>
       </c>
       <c r="G278" t="n">
-        <v>0.20597068965435</v>
+        <v>0.205970704555511</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0.244751006364822</v>
       </c>
       <c r="G279" t="n">
-        <v>0.20597068965435</v>
+        <v>0.205970704555511</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>0.234760999679565</v>
       </c>
       <c r="G282" t="n">
-        <v>0.197563588619232</v>
+        <v>0.197563573718071</v>
       </c>
       <c r="H282" t="n">
         <v>5084</v>
@@ -8576,7 +8576,7 @@
         <v>0.234760999679565</v>
       </c>
       <c r="G283" t="n">
-        <v>0.197563588619232</v>
+        <v>0.197563573718071</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>0.229765996336937</v>
       </c>
       <c r="G284" t="n">
-        <v>0.193360045552254</v>
+        <v>0.193360030651093</v>
       </c>
       <c r="H284" t="n">
         <v>10010</v>
@@ -9823,7 +9823,7 @@
         <v>0.250445008277893</v>
       </c>
       <c r="G326" t="n">
-        <v>0.210762500762939</v>
+        <v>0.210762515664101</v>
       </c>
       <c r="H326" t="n">
         <v>1001</v>
@@ -9852,7 +9852,7 @@
         <v>0.255739986896515</v>
       </c>
       <c r="G327" t="n">
-        <v>0.215218514204025</v>
+        <v>0.215218499302864</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -10026,7 +10026,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G333" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H333" t="n">
         <v>500</v>
@@ -10055,7 +10055,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G334" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G335" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G336" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G337" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G338" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G339" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G340" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G341" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G342" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G343" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G344" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G345" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G346" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>0.275718986988068</v>
       </c>
       <c r="G347" t="n">
-        <v>0.232031866908073</v>
+        <v>0.232031881809235</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G359" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10809,7 +10809,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G360" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G361" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G362" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G363" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G364" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>0.29170298576355</v>
       </c>
       <c r="G365" t="n">
-        <v>0.245483219623566</v>
+        <v>0.245483249425888</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G381" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H381" t="n">
         <v>2502</v>
@@ -11447,7 +11447,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G382" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G383" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G384" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G385" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>0.306688010692596</v>
       </c>
       <c r="G386" t="n">
-        <v>0.258093893527985</v>
+        <v>0.258093923330307</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>0.361631989479065</v>
       </c>
       <c r="G406" t="n">
-        <v>0.304332137107849</v>
+        <v>0.304332107305527</v>
       </c>
       <c r="H406" t="n">
         <v>500</v>
@@ -12230,7 +12230,7 @@
         <v>0.377315998077393</v>
       </c>
       <c r="G409" t="n">
-        <v>0.317531019449234</v>
+        <v>0.317531049251556</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -12317,7 +12317,7 @@
         <v>0.399594008922577</v>
       </c>
       <c r="G412" t="n">
-        <v>0.336279153823853</v>
+        <v>0.33627912402153</v>
       </c>
       <c r="H412" t="n">
         <v>1001</v>
@@ -12346,7 +12346,7 @@
         <v>0.399594008922577</v>
       </c>
       <c r="G413" t="n">
-        <v>0.336279153823853</v>
+        <v>0.33627912402153</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>0.399594008922577</v>
       </c>
       <c r="G414" t="n">
-        <v>0.336279153823853</v>
+        <v>0.33627912402153</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>0.399594008922577</v>
       </c>
       <c r="G415" t="n">
-        <v>0.336279153823853</v>
+        <v>0.33627912402153</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>0.399594008922577</v>
       </c>
       <c r="G416" t="n">
-        <v>0.336279153823853</v>
+        <v>0.33627912402153</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -12549,7 +12549,7 @@
         <v>0.43156099319458</v>
       </c>
       <c r="G420" t="n">
-        <v>0.36318102478981</v>
+        <v>0.363180994987488</v>
       </c>
       <c r="H420" t="n">
         <v>1</v>
@@ -12578,7 +12578,7 @@
         <v>0.449542999267578</v>
       </c>
       <c r="G421" t="n">
-        <v>0.378313779830933</v>
+        <v>0.378313809633255</v>
       </c>
       <c r="H421" t="n">
         <v>210</v>
@@ -12607,7 +12607,7 @@
         <v>0.489502012729645</v>
       </c>
       <c r="G422" t="n">
-        <v>0.411941379308701</v>
+        <v>0.411941409111023</v>
       </c>
       <c r="H422" t="n">
         <v>1069</v>
@@ -12752,7 +12752,7 @@
         <v>0.574415981769562</v>
       </c>
       <c r="G427" t="n">
-        <v>0.483400911092758</v>
+        <v>0.483400970697403</v>
       </c>
       <c r="H427" t="n">
         <v>500</v>
@@ -15246,7 +15246,7 @@
         <v>0.594395995140076</v>
       </c>
       <c r="G513" t="n">
-        <v>0.500215113162994</v>
+        <v>0.500215172767639</v>
       </c>
       <c r="H513" t="n">
         <v>5005</v>
@@ -15275,7 +15275,7 @@
         <v>0.594395995140076</v>
       </c>
       <c r="G514" t="n">
-        <v>0.500215113162994</v>
+        <v>0.500215172767639</v>
       </c>
       <c r="H514" t="n">
         <v>10</v>
@@ -15304,7 +15304,7 @@
         <v>0.594395995140076</v>
       </c>
       <c r="G515" t="n">
-        <v>0.500215113162994</v>
+        <v>0.500215172767639</v>
       </c>
       <c r="H515" t="n">
         <v>2870</v>
@@ -15333,7 +15333,7 @@
         <v>0.594395995140076</v>
       </c>
       <c r="G516" t="n">
-        <v>0.500215113162994</v>
+        <v>0.500215172767639</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G552" t="n">
-        <v>0.492307931184769</v>
+        <v>0.492307990789413</v>
       </c>
       <c r="H552" t="n">
         <v>12500</v>
@@ -16406,7 +16406,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G553" t="n">
-        <v>0.492307931184769</v>
+        <v>0.492307990789413</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G554" t="n">
-        <v>0.492307931184769</v>
+        <v>0.492307990789413</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G559" t="n">
-        <v>0.67324161529541</v>
+        <v>0.673241674900055</v>
       </c>
       <c r="H559" t="n">
         <v>110992</v>
@@ -16638,7 +16638,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G561" t="n">
-        <v>0.618540704250336</v>
+        <v>0.61854076385498</v>
       </c>
       <c r="H561" t="n">
         <v>21790</v>
@@ -16667,7 +16667,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>0.62274843454361</v>
+        <v>0.622748494148254</v>
       </c>
       <c r="H562" t="n">
         <v>26516</v>
@@ -16841,7 +16841,7 @@
         <v>0.625</v>
       </c>
       <c r="G568" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H568" t="n">
         <v>26958</v>
@@ -16870,7 +16870,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H569" t="n">
         <v>10440</v>
@@ -16899,7 +16899,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G571" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G573" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H573" t="n">
         <v>6100</v>
@@ -17015,7 +17015,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G574" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.492307931184769</v>
+        <v>0.492307990789413</v>
       </c>
       <c r="H590" t="n">
         <v>6921</v>
@@ -17537,7 +17537,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G592" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H592" t="n">
         <v>517</v>
@@ -17566,7 +17566,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G593" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G594" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G595" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G596" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H597" t="n">
         <v>200</v>
@@ -17711,7 +17711,7 @@
         <v>0.625</v>
       </c>
       <c r="G598" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>0.625</v>
       </c>
       <c r="G599" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H600" t="n">
         <v>4000</v>
@@ -17798,7 +17798,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G601" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>0.625</v>
       </c>
       <c r="G602" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H602" t="n">
         <v>3500</v>
@@ -17856,7 +17856,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G603" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H603" t="n">
         <v>3100</v>
@@ -17885,7 +17885,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G604" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G605" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>0.625</v>
       </c>
       <c r="G606" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H606" t="n">
         <v>2151</v>
@@ -17972,7 +17972,7 @@
         <v>0.625</v>
       </c>
       <c r="G607" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>0.625</v>
       </c>
       <c r="G608" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H608" t="n">
         <v>0</v>
@@ -18030,7 +18030,7 @@
         <v>0.625</v>
       </c>
       <c r="G609" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H609" t="n">
         <v>800</v>
@@ -18059,7 +18059,7 @@
         <v>0.625</v>
       </c>
       <c r="G610" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18146,7 +18146,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H613" t="n">
         <v>4000</v>
@@ -18523,7 +18523,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G626" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H626" t="n">
         <v>2107</v>
@@ -19074,7 +19074,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G645" t="n">
-        <v>0.492307931184769</v>
+        <v>0.492307990789413</v>
       </c>
       <c r="H645" t="n">
         <v>777</v>
@@ -19103,7 +19103,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G646" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H646" t="n">
         <v>7797</v>
@@ -19161,7 +19161,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G648" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H648" t="n">
         <v>7047</v>
@@ -19190,7 +19190,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G649" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G653" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H653" t="n">
         <v>20000</v>
@@ -19335,7 +19335,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G654" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H654" t="n">
         <v>1190</v>
@@ -19364,7 +19364,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G655" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H655" t="n">
         <v>6150</v>
@@ -19393,7 +19393,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G656" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H656" t="n">
         <v>2200</v>
@@ -19567,7 +19567,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G662" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H662" t="n">
         <v>81</v>
@@ -19596,7 +19596,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G663" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G664" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G679" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H679" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G680" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G681" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G682" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G683" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G684" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20234,7 +20234,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G685" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G686" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H686" t="n">
         <v>925</v>
@@ -20292,7 +20292,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G687" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H687" t="n">
         <v>625</v>
@@ -20321,7 +20321,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G688" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H688" t="n">
         <v>4200</v>
@@ -20350,7 +20350,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G689" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G690" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H690" t="n">
         <v>1820</v>
@@ -20408,7 +20408,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G691" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G692" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G693" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G694" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H694" t="n">
         <v>960</v>
@@ -20524,7 +20524,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G695" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G696" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G697" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -20611,7 +20611,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G698" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G699" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G700" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H700" t="n">
         <v>2000</v>
@@ -20698,7 +20698,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G701" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H701" t="n">
         <v>2000</v>
@@ -20727,7 +20727,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G702" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G703" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H703" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G704" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G723" t="n">
-        <v>0.534385561943054</v>
+        <v>0.534385502338409</v>
       </c>
       <c r="H723" t="n">
         <v>53025</v>
@@ -21365,7 +21365,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>0.534385561943054</v>
+        <v>0.534385502338409</v>
       </c>
       <c r="H724" t="n">
         <v>17823</v>
@@ -21539,7 +21539,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G730" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H730" t="n">
         <v>481</v>
@@ -21684,7 +21684,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H735" t="n">
         <v>16220</v>
@@ -21713,7 +21713,7 @@
         <v>0.625</v>
       </c>
       <c r="G736" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H736" t="n">
         <v>1109</v>
@@ -21742,7 +21742,7 @@
         <v>0.625</v>
       </c>
       <c r="G737" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H737" t="n">
         <v>3400</v>
@@ -21771,7 +21771,7 @@
         <v>0.625</v>
       </c>
       <c r="G738" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H738" t="n">
         <v>500</v>
@@ -21800,7 +21800,7 @@
         <v>0.625</v>
       </c>
       <c r="G739" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H739" t="n">
         <v>1500</v>
@@ -21829,7 +21829,7 @@
         <v>0.625</v>
       </c>
       <c r="G740" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>0.625</v>
       </c>
       <c r="G741" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -21887,7 +21887,7 @@
         <v>0.625</v>
       </c>
       <c r="G742" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -21916,7 +21916,7 @@
         <v>0.625</v>
       </c>
       <c r="G743" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>0.625</v>
       </c>
       <c r="G744" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H744" t="n">
         <v>3000</v>
@@ -22061,7 +22061,7 @@
         <v>0.625</v>
       </c>
       <c r="G748" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H748" t="n">
         <v>1833</v>
@@ -22090,7 +22090,7 @@
         <v>0.625</v>
       </c>
       <c r="G749" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>0.625</v>
       </c>
       <c r="G750" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>0.625</v>
       </c>
       <c r="G751" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H751" t="n">
         <v>10250</v>
@@ -22177,7 +22177,7 @@
         <v>0.625</v>
       </c>
       <c r="G752" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>0.625</v>
       </c>
       <c r="G753" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>0.625</v>
       </c>
       <c r="G754" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G755" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H755" t="n">
         <v>12094</v>
@@ -22293,7 +22293,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G756" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G758" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H758" t="n">
         <v>2001</v>
@@ -22380,7 +22380,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G759" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G760" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G761" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22902,7 +22902,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G777" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H777" t="n">
         <v>11000</v>
@@ -22931,7 +22931,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G778" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H778" t="n">
         <v>7429</v>
@@ -23801,7 +23801,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G808" t="n">
-        <v>0.380381494760513</v>
+        <v>0.380381524562836</v>
       </c>
       <c r="H808" t="n">
         <v>2460</v>
@@ -23830,7 +23830,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G809" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H809" t="n">
         <v>30422</v>
@@ -24004,7 +24004,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G815" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H815" t="n">
         <v>4063</v>
@@ -24033,7 +24033,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G816" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -24062,7 +24062,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G817" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H817" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G818" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H818" t="n">
         <v>11440</v>
@@ -24729,7 +24729,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G840" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H840" t="n">
         <v>3818</v>
@@ -24874,7 +24874,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G845" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H845" t="n">
         <v>14189</v>
@@ -26643,7 +26643,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G906" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H906" t="n">
         <v>19728</v>
@@ -26672,7 +26672,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G907" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H907" t="n">
         <v>3367</v>
@@ -26701,7 +26701,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G908" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G913" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H913" t="n">
         <v>48</v>
@@ -26875,7 +26875,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G914" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G915" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G916" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G917" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G918" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G919" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G929" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H929" t="n">
         <v>600</v>
@@ -28151,7 +28151,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G958" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H958" t="n">
         <v>13283</v>
@@ -28238,7 +28238,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G961" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H961" t="n">
         <v>22719</v>
@@ -28673,7 +28673,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G976" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H976" t="n">
         <v>3621</v>
@@ -28847,7 +28847,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G982" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H982" t="n">
         <v>12589</v>
@@ -28934,7 +28934,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G985" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H985" t="n">
         <v>21</v>
@@ -28963,7 +28963,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G986" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H986" t="n">
         <v>1500</v>
@@ -29108,7 +29108,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G991" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H991" t="n">
         <v>21</v>
@@ -29311,7 +29311,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G998" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H998" t="n">
         <v>10198</v>
@@ -29340,7 +29340,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G999" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1031" t="n">
         <v>445386</v>
@@ -30384,7 +30384,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1035" t="n">
         <v>85860</v>
@@ -30935,7 +30935,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1054" t="n">
         <v>15804</v>
@@ -30964,7 +30964,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1055" t="n">
         <v>22070</v>
@@ -31167,7 +31167,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.373649120330811</v>
+        <v>0.373649090528488</v>
       </c>
       <c r="H1062" t="n">
         <v>206222</v>
@@ -31225,7 +31225,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.311374217271805</v>
+        <v>0.311374247074127</v>
       </c>
       <c r="H1064" t="n">
         <v>91098</v>
@@ -31254,7 +31254,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.336620807647705</v>
+        <v>0.336620837450027</v>
       </c>
       <c r="H1065" t="n">
         <v>2700</v>
@@ -31283,7 +31283,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.336620807647705</v>
+        <v>0.336620837450027</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -31399,7 +31399,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1070" t="n">
         <v>6212</v>
@@ -31428,7 +31428,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -31457,7 +31457,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -31486,7 +31486,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.324839055538177</v>
+        <v>0.3248390853405</v>
       </c>
       <c r="H1073" t="n">
         <v>9800</v>
@@ -31573,7 +31573,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.351768732070923</v>
+        <v>0.351768761873245</v>
       </c>
       <c r="H1076" t="n">
         <v>1701</v>
@@ -31718,7 +31718,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.336620807647705</v>
+        <v>0.336620837450027</v>
       </c>
       <c r="H1081" t="n">
         <v>102477</v>
@@ -31776,7 +31776,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.336620807647705</v>
+        <v>0.336620837450027</v>
       </c>
       <c r="H1083" t="n">
         <v>14682</v>
@@ -31805,7 +31805,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.336620807647705</v>
+        <v>0.336620837450027</v>
       </c>
       <c r="H1084" t="n">
         <v>286185</v>
@@ -31834,7 +31834,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.350085616111755</v>
+        <v>0.350085645914078</v>
       </c>
       <c r="H1085" t="n">
         <v>51321</v>
@@ -31950,7 +31950,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.343353241682053</v>
+        <v>0.34335321187973</v>
       </c>
       <c r="H1089" t="n">
         <v>20598</v>
@@ -31979,7 +31979,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.343353241682053</v>
+        <v>0.34335321187973</v>
       </c>
       <c r="H1090" t="n">
         <v>0</v>
@@ -32008,7 +32008,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.333254635334015</v>
+        <v>0.333254605531693</v>
       </c>
       <c r="H1091" t="n">
         <v>30498</v>
@@ -32066,7 +32066,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.324839055538177</v>
+        <v>0.3248390853405</v>
       </c>
       <c r="H1093" t="n">
         <v>101330</v>
@@ -32095,7 +32095,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.333254635334015</v>
+        <v>0.333254605531693</v>
       </c>
       <c r="H1094" t="n">
         <v>38028</v>
@@ -32124,7 +32124,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1095" t="n">
         <v>62645</v>
@@ -32298,7 +32298,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.324839055538177</v>
+        <v>0.3248390853405</v>
       </c>
       <c r="H1101" t="n">
         <v>274057</v>
@@ -32327,7 +32327,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1102" t="n">
         <v>1027</v>
@@ -32501,7 +32501,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1108" t="n">
         <v>35538</v>
@@ -32530,7 +32530,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.326522171497345</v>
+        <v>0.326522201299667</v>
       </c>
       <c r="H1109" t="n">
         <v>3501</v>
@@ -32704,7 +32704,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.333254635334015</v>
+        <v>0.333254605531693</v>
       </c>
       <c r="H1115" t="n">
         <v>29599</v>
@@ -32791,7 +32791,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.366916686296463</v>
+        <v>0.366916656494141</v>
       </c>
       <c r="H1118" t="n">
         <v>48373</v>
@@ -32820,7 +32820,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.366916686296463</v>
+        <v>0.366916656494141</v>
       </c>
       <c r="H1119" t="n">
         <v>169051</v>
@@ -32849,7 +32849,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.366916686296463</v>
+        <v>0.366916656494141</v>
       </c>
       <c r="H1120" t="n">
         <v>0</v>
@@ -33052,7 +33052,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.397212564945221</v>
+        <v>0.397212535142899</v>
       </c>
       <c r="H1127" t="n">
         <v>1600</v>
@@ -33081,7 +33081,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.397212564945221</v>
+        <v>0.397212535142899</v>
       </c>
       <c r="H1128" t="n">
         <v>14646</v>
@@ -33168,7 +33168,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.380381494760513</v>
+        <v>0.380381524562836</v>
       </c>
       <c r="H1131" t="n">
         <v>4440</v>
@@ -33487,7 +33487,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1142" t="n">
         <v>16383</v>
@@ -33516,7 +33516,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.373649120330811</v>
+        <v>0.373649090528488</v>
       </c>
       <c r="H1143" t="n">
         <v>10680</v>
@@ -33545,7 +33545,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1144" t="n">
         <v>6000</v>
@@ -33632,7 +33632,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1147" t="n">
         <v>200</v>
@@ -33690,7 +33690,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1149" t="n">
         <v>300</v>
@@ -33719,7 +33719,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1150" t="n">
         <v>2098</v>
@@ -33748,7 +33748,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.371966004371643</v>
+        <v>0.371965974569321</v>
       </c>
       <c r="H1151" t="n">
         <v>38022</v>
@@ -33835,7 +33835,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1154" t="n">
         <v>100</v>
@@ -33951,7 +33951,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1158" t="n">
         <v>16090</v>
@@ -34067,7 +34067,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.371966004371643</v>
+        <v>0.371965974569321</v>
       </c>
       <c r="H1162" t="n">
         <v>16089</v>
@@ -34299,7 +34299,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1170" t="n">
         <v>1000</v>
@@ -34328,7 +34328,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34386,7 +34386,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1173" t="n">
         <v>999</v>
@@ -34415,7 +34415,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.378698378801346</v>
+        <v>0.378698408603668</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34502,7 +34502,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.371966004371643</v>
+        <v>0.371965974569321</v>
       </c>
       <c r="H1177" t="n">
         <v>6300</v>
@@ -34676,7 +34676,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.366916686296463</v>
+        <v>0.366916656494141</v>
       </c>
       <c r="H1183" t="n">
         <v>1552024</v>
@@ -34705,7 +34705,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.377015322446823</v>
+        <v>0.377015292644501</v>
       </c>
       <c r="H1184" t="n">
         <v>32900</v>
@@ -34850,7 +34850,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H1189" t="n">
         <v>161095</v>
@@ -34908,7 +34908,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H1191" t="n">
         <v>217315</v>
@@ -34937,7 +34937,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1192" t="n">
         <v>121882</v>
@@ -34966,7 +34966,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1193" t="n">
         <v>43996</v>
@@ -34995,7 +34995,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1194" t="n">
         <v>0</v>
@@ -35024,7 +35024,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H1195" t="n">
         <v>50854</v>
@@ -35256,7 +35256,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H1203" t="n">
         <v>16574</v>
@@ -35691,7 +35691,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1218" t="n">
         <v>124593</v>
@@ -35720,7 +35720,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.415726691484451</v>
+        <v>0.415726721286774</v>
       </c>
       <c r="H1219" t="n">
         <v>0</v>
@@ -35778,7 +35778,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H1221" t="n">
         <v>43150</v>
@@ -36068,7 +36068,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H1231" t="n">
         <v>400</v>
@@ -36097,7 +36097,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H1232" t="n">
         <v>0</v>
@@ -36126,7 +36126,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.414043575525284</v>
+        <v>0.414043605327606</v>
       </c>
       <c r="H1233" t="n">
         <v>0</v>
@@ -36155,7 +36155,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.407311201095581</v>
+        <v>0.407311171293259</v>
       </c>
       <c r="H1234" t="n">
         <v>11770</v>
@@ -36880,7 +36880,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1259" t="n">
         <v>61313</v>
@@ -36996,7 +36996,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H1263" t="n">
         <v>225009</v>
@@ -37344,7 +37344,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.551216542720795</v>
+        <v>0.551216602325439</v>
       </c>
       <c r="H1275" t="n">
         <v>20833</v>
@@ -37460,7 +37460,7 @@
         <v>0.625</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H1279" t="n">
         <v>152813</v>
@@ -37489,7 +37489,7 @@
         <v>0.625</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.525970041751862</v>
+        <v>0.525969982147217</v>
       </c>
       <c r="H1280" t="n">
         <v>37091</v>
@@ -37663,7 +37663,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H1286" t="n">
         <v>230961</v>
@@ -38011,7 +38011,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1298" t="n">
         <v>156143</v>
@@ -38040,7 +38040,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1299" t="n">
         <v>214495</v>
@@ -38069,7 +38069,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H1300" t="n">
         <v>112502</v>
@@ -38098,7 +38098,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1301" t="n">
         <v>961410</v>
@@ -38127,7 +38127,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1302" t="n">
         <v>1241491</v>
@@ -38156,7 +38156,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1303" t="n">
         <v>31468</v>
@@ -38185,7 +38185,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1304" t="n">
         <v>26845</v>
@@ -38272,7 +38272,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1307" t="n">
         <v>38734</v>
@@ -38330,7 +38330,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1309" t="n">
         <v>189642</v>
@@ -38388,7 +38388,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1311" t="n">
         <v>153824</v>
@@ -38417,7 +38417,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1312" t="n">
         <v>26300</v>
@@ -38446,7 +38446,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1313" t="n">
         <v>34809</v>
@@ -38504,7 +38504,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1315" t="n">
         <v>48389</v>
@@ -38533,7 +38533,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1316" t="n">
         <v>1802</v>
@@ -38562,7 +38562,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1317" t="n">
         <v>14721</v>
@@ -38591,7 +38591,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1318" t="n">
         <v>17818</v>
@@ -38620,7 +38620,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1319" t="n">
         <v>86177</v>
@@ -38649,7 +38649,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1320" t="n">
         <v>0</v>
@@ -38678,7 +38678,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1321" t="n">
         <v>33204</v>
@@ -38736,7 +38736,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1323" t="n">
         <v>5000</v>
@@ -38765,7 +38765,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.454438120126724</v>
+        <v>0.454438090324402</v>
       </c>
       <c r="H1324" t="n">
         <v>19334</v>
@@ -38794,7 +38794,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1325" t="n">
         <v>8018</v>
@@ -38852,7 +38852,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1327" t="n">
         <v>16460</v>
@@ -38881,7 +38881,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.462853610515594</v>
+        <v>0.462853640317917</v>
       </c>
       <c r="H1328" t="n">
         <v>13000</v>
@@ -38939,7 +38939,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.475476920604706</v>
+        <v>0.475476861000061</v>
       </c>
       <c r="H1330" t="n">
         <v>21800</v>
@@ -39113,7 +39113,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.48473396897316</v>
+        <v>0.484733909368515</v>
       </c>
       <c r="H1336" t="n">
         <v>35851</v>
@@ -39171,7 +39171,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.471269071102142</v>
+        <v>0.471269130706787</v>
       </c>
       <c r="H1338" t="n">
         <v>15249</v>
@@ -39490,7 +39490,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H1349" t="n">
         <v>58398</v>
@@ -39635,7 +39635,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.523445308208466</v>
+        <v>0.52344536781311</v>
       </c>
       <c r="H1354" t="n">
         <v>26616</v>
@@ -39664,7 +39664,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.50661438703537</v>
+        <v>0.506614327430725</v>
       </c>
       <c r="H1355" t="n">
         <v>344375</v>
@@ -39780,7 +39780,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H1359" t="n">
         <v>7550</v>
@@ -39925,7 +39925,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.504931211471558</v>
+        <v>0.504931151866913</v>
       </c>
       <c r="H1364" t="n">
         <v>73200</v>
@@ -40070,7 +40070,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.50661438703537</v>
+        <v>0.506614327430725</v>
       </c>
       <c r="H1369" t="n">
         <v>51065</v>
@@ -40331,7 +40331,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1378" t="n">
         <v>1693418</v>
@@ -40476,7 +40476,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.557107508182526</v>
+        <v>0.557107448577881</v>
       </c>
       <c r="H1383" t="n">
         <v>808738</v>
@@ -40650,7 +40650,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.531860828399658</v>
+        <v>0.531860888004303</v>
       </c>
       <c r="H1389" t="n">
         <v>76445</v>
@@ -40708,7 +40708,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.523445308208466</v>
+        <v>0.52344536781311</v>
       </c>
       <c r="H1391" t="n">
         <v>149650</v>
@@ -40737,7 +40737,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1392" t="n">
         <v>71368</v>
@@ -40766,7 +40766,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1393" t="n">
         <v>58543</v>
@@ -40882,7 +40882,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.523445308208466</v>
+        <v>0.52344536781311</v>
       </c>
       <c r="H1397" t="n">
         <v>346565</v>
@@ -41143,7 +41143,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.523445308208466</v>
+        <v>0.52344536781311</v>
       </c>
       <c r="H1406" t="n">
         <v>3026</v>
@@ -41172,7 +41172,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.521762192249298</v>
+        <v>0.521762251853943</v>
       </c>
       <c r="H1407" t="n">
         <v>4181</v>
@@ -41288,7 +41288,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1411" t="n">
         <v>179815</v>
@@ -41346,7 +41346,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.531860828399658</v>
+        <v>0.531860888004303</v>
       </c>
       <c r="H1413" t="n">
         <v>17843</v>
@@ -41404,7 +41404,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.531860828399658</v>
+        <v>0.531860888004303</v>
       </c>
       <c r="H1415" t="n">
         <v>210032</v>
@@ -41462,7 +41462,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1417" t="n">
         <v>129113</v>
@@ -41491,7 +41491,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.533543884754181</v>
+        <v>0.533543944358826</v>
       </c>
       <c r="H1418" t="n">
         <v>143063</v>
@@ -42129,7 +42129,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.549185335636139</v>
+        <v>0.549185395240784</v>
       </c>
       <c r="H1440" t="n">
         <v>33697</v>
@@ -42506,7 +42506,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.549185335636139</v>
+        <v>0.549185395240784</v>
       </c>
       <c r="H1453" t="n">
         <v>44216</v>
@@ -42680,7 +42680,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.540495634078979</v>
+        <v>0.540495693683624</v>
       </c>
       <c r="H1459" t="n">
         <v>48500</v>
@@ -42999,7 +42999,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.540495634078979</v>
+        <v>0.540495693683624</v>
       </c>
       <c r="H1470" t="n">
         <v>38900</v>
@@ -43463,7 +43463,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.549185335636139</v>
+        <v>0.549185395240784</v>
       </c>
       <c r="H1486" t="n">
         <v>45404</v>
@@ -43492,7 +43492,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.550923228263855</v>
+        <v>0.5509232878685</v>
       </c>
       <c r="H1487" t="n">
         <v>58592</v>
@@ -43521,7 +43521,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.540495634078979</v>
+        <v>0.540495693683624</v>
       </c>
       <c r="H1488" t="n">
         <v>71511</v>
@@ -43695,7 +43695,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1494" t="n">
         <v>120180</v>
@@ -43753,7 +43753,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.512688875198364</v>
+        <v>0.512688815593719</v>
       </c>
       <c r="H1496" t="n">
         <v>209659</v>
@@ -43782,7 +43782,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.512688875198364</v>
+        <v>0.512688815593719</v>
       </c>
       <c r="H1497" t="n">
         <v>98033</v>
@@ -43811,7 +43811,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.512688875198364</v>
+        <v>0.512688815593719</v>
       </c>
       <c r="H1498" t="n">
         <v>9933</v>
@@ -43927,7 +43927,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1502" t="n">
         <v>130100</v>
@@ -44159,7 +44159,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1510" t="n">
         <v>75470</v>
@@ -44246,7 +44246,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1513" t="n">
         <v>62515</v>
@@ -44275,7 +44275,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.52311646938324</v>
+        <v>0.523116409778595</v>
       </c>
       <c r="H1514" t="n">
         <v>22406</v>
@@ -44304,7 +44304,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.52311646938324</v>
+        <v>0.523116409778595</v>
       </c>
       <c r="H1515" t="n">
         <v>0</v>
@@ -44362,7 +44362,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1517" t="n">
         <v>1500</v>
@@ -44391,7 +44391,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.52311646938324</v>
+        <v>0.523116409778595</v>
       </c>
       <c r="H1518" t="n">
         <v>7501</v>
@@ -44420,7 +44420,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1519" t="n">
         <v>3844</v>
@@ -44449,7 +44449,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.512688875198364</v>
+        <v>0.512688815593719</v>
       </c>
       <c r="H1520" t="n">
         <v>88</v>
@@ -44478,7 +44478,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1521" t="n">
         <v>22034</v>
@@ -44507,7 +44507,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1522" t="n">
         <v>33543</v>
@@ -44536,7 +44536,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1523" t="n">
         <v>20500</v>
@@ -44565,7 +44565,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1524" t="n">
         <v>21122</v>
@@ -44594,7 +44594,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.521378517150879</v>
+        <v>0.521378457546234</v>
       </c>
       <c r="H1525" t="n">
         <v>39172</v>
@@ -44623,7 +44623,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.540495634078979</v>
+        <v>0.540495693683624</v>
       </c>
       <c r="H1526" t="n">
         <v>196467</v>
@@ -44681,7 +44681,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.587419807910919</v>
+        <v>0.587419748306274</v>
       </c>
       <c r="H1528" t="n">
         <v>1379662</v>
@@ -44710,7 +44710,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.601323187351227</v>
+        <v>0.601323246955872</v>
       </c>
       <c r="H1529" t="n">
         <v>720073</v>
@@ -44855,7 +44855,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.587419807910919</v>
+        <v>0.587419748306274</v>
       </c>
       <c r="H1534" t="n">
         <v>96273</v>
@@ -45145,7 +45145,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.627392113208771</v>
+        <v>0.627392053604126</v>
       </c>
       <c r="H1544" t="n">
         <v>419344</v>
@@ -45174,7 +45174,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.618702471256256</v>
+        <v>0.618702530860901</v>
       </c>
       <c r="H1545" t="n">
         <v>62569</v>
@@ -45319,7 +45319,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.644771456718445</v>
+        <v>0.6447713971138</v>
       </c>
       <c r="H1550" t="n">
         <v>78046</v>
@@ -45435,7 +45435,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.644771456718445</v>
+        <v>0.6447713971138</v>
       </c>
       <c r="H1554" t="n">
         <v>168777</v>
@@ -45493,7 +45493,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.643033444881439</v>
+        <v>0.643033504486084</v>
       </c>
       <c r="H1556" t="n">
         <v>34141</v>
@@ -45551,7 +45551,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.622178316116333</v>
+        <v>0.622178375720978</v>
       </c>
       <c r="H1558" t="n">
         <v>259787</v>
@@ -45580,7 +45580,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.618702471256256</v>
+        <v>0.618702530860901</v>
       </c>
       <c r="H1559" t="n">
         <v>145055</v>
@@ -45667,7 +45667,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.610012829303741</v>
+        <v>0.610012888908386</v>
       </c>
       <c r="H1562" t="n">
         <v>157798</v>
@@ -45696,7 +45696,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.601323187351227</v>
+        <v>0.601323246955872</v>
       </c>
       <c r="H1563" t="n">
         <v>119397</v>
@@ -45754,7 +45754,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.583943903446198</v>
+        <v>0.583943843841553</v>
       </c>
       <c r="H1565" t="n">
         <v>431015</v>
@@ -45899,7 +45899,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.582206010818481</v>
+        <v>0.582205951213837</v>
       </c>
       <c r="H1570" t="n">
         <v>560241</v>
@@ -46102,7 +46102,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.550923228263855</v>
+        <v>0.5509232878685</v>
       </c>
       <c r="H1577" t="n">
         <v>88104</v>
@@ -46247,7 +46247,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.582206010818481</v>
+        <v>0.582205951213837</v>
       </c>
       <c r="H1582" t="n">
         <v>46976</v>
@@ -46334,7 +46334,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.601323187351227</v>
+        <v>0.601323246955872</v>
       </c>
       <c r="H1585" t="n">
         <v>645632</v>
@@ -46450,7 +46450,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.648247241973877</v>
+        <v>0.648247182369232</v>
       </c>
       <c r="H1589" t="n">
         <v>2500466</v>
@@ -46479,7 +46479,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.636081755161285</v>
+        <v>0.636081695556641</v>
       </c>
       <c r="H1590" t="n">
         <v>176884</v>
@@ -46508,7 +46508,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.636081755161285</v>
+        <v>0.636081695556641</v>
       </c>
       <c r="H1591" t="n">
         <v>128852</v>
@@ -46537,7 +46537,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.683005809783936</v>
+        <v>0.68300586938858</v>
       </c>
       <c r="H1592" t="n">
         <v>1028370</v>
@@ -46595,7 +46595,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.688219666481018</v>
+        <v>0.688219606876373</v>
       </c>
       <c r="H1594" t="n">
         <v>358711</v>
@@ -46682,7 +46682,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.662150681018829</v>
+        <v>0.662150740623474</v>
       </c>
       <c r="H1597" t="n">
         <v>316152</v>
@@ -46711,7 +46711,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.674316167831421</v>
+        <v>0.674316227436066</v>
       </c>
       <c r="H1598" t="n">
         <v>428681</v>
@@ -46914,7 +46914,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.658674776554108</v>
+        <v>0.658674836158752</v>
       </c>
       <c r="H1605" t="n">
         <v>79111</v>
@@ -46943,7 +46943,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.643033444881439</v>
+        <v>0.643033504486084</v>
       </c>
       <c r="H1606" t="n">
         <v>88422</v>
@@ -46972,7 +46972,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.643033444881439</v>
+        <v>0.643033504486084</v>
       </c>
       <c r="H1607" t="n">
         <v>111714</v>
@@ -47059,7 +47059,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.648247241973877</v>
+        <v>0.648247182369232</v>
       </c>
       <c r="H1610" t="n">
         <v>12126</v>
@@ -47117,7 +47117,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.644771456718445</v>
+        <v>0.6447713971138</v>
       </c>
       <c r="H1612" t="n">
         <v>98209</v>
@@ -47320,7 +47320,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.618702471256256</v>
+        <v>0.618702530860901</v>
       </c>
       <c r="H1619" t="n">
         <v>15500</v>
@@ -47349,7 +47349,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.622178316116333</v>
+        <v>0.622178375720978</v>
       </c>
       <c r="H1620" t="n">
         <v>3009</v>
@@ -47378,7 +47378,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.636081755161285</v>
+        <v>0.636081695556641</v>
       </c>
       <c r="H1621" t="n">
         <v>159304</v>
@@ -47436,7 +47436,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.615226626396179</v>
+        <v>0.615226566791534</v>
       </c>
       <c r="H1623" t="n">
         <v>115253</v>
@@ -47465,7 +47465,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.615226626396179</v>
+        <v>0.615226566791534</v>
       </c>
       <c r="H1624" t="n">
         <v>49145</v>
@@ -80038,6 +80038,35 @@
         <v>27351</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.751999974250793</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.734000027179718</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1367</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.280214995145798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.235815480351448</v>
+        <v>0.235815465450287</v>
       </c>
       <c r="H2" t="n">
         <v>11110</v>
@@ -456,7 +456,7 @@
         <v>0.280214995145798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.235815480351448</v>
+        <v>0.235815465450287</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>0.280214995145798</v>
       </c>
       <c r="G4" t="n">
-        <v>0.235815480351448</v>
+        <v>0.235815465450287</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H7" t="n">
         <v>9139</v>
@@ -601,7 +601,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H8" t="n">
         <v>6006</v>
@@ -630,7 +630,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G9" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G11" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G12" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G13" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H13" t="n">
         <v>9880</v>
@@ -775,7 +775,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G14" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G15" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G16" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G17" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G18" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G20" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.271223992109299</v>
       </c>
       <c r="G21" t="n">
-        <v>0.228249132633209</v>
+        <v>0.228249117732048</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G22" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H22" t="n">
         <v>512</v>
@@ -1152,7 +1152,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G27" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H27" t="n">
         <v>5005</v>
@@ -1181,7 +1181,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G28" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H28" t="n">
         <v>1501</v>
@@ -1210,7 +1210,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G29" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G30" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H30" t="n">
         <v>3503</v>
@@ -1268,7 +1268,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G31" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H31" t="n">
         <v>5924</v>
@@ -1297,7 +1297,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G32" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G33" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G34" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G35" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G36" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G37" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G38" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0.257737994194031</v>
       </c>
       <c r="G39" t="n">
-        <v>0.216899931430817</v>
+        <v>0.216899946331978</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G73" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H73" t="n">
         <v>159</v>
@@ -2515,7 +2515,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G74" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G75" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G76" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G77" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G78" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G79" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G80" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G81" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G82" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G83" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G84" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>0.277218014001846</v>
       </c>
       <c r="G85" t="n">
-        <v>0.233293354511261</v>
+        <v>0.233293369412422</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0.275119990110397</v>
       </c>
       <c r="G91" t="n">
-        <v>0.231527790427208</v>
+        <v>0.231527805328369</v>
       </c>
       <c r="H91" t="n">
         <v>107</v>
@@ -3037,7 +3037,7 @@
         <v>0.275119990110397</v>
       </c>
       <c r="G92" t="n">
-        <v>0.231527790427208</v>
+        <v>0.231527805328369</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.275119990110397</v>
       </c>
       <c r="G93" t="n">
-        <v>0.231527790427208</v>
+        <v>0.231527805328369</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G151" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H151" t="n">
         <v>11211</v>
@@ -4777,7 +4777,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G152" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G153" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G154" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G155" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G156" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G157" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G158" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G159" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G160" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G161" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G162" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G163" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G164" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G165" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G166" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G167" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>0.273021996021271</v>
       </c>
       <c r="G168" t="n">
-        <v>0.229762196540833</v>
+        <v>0.229762211441994</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G169" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H169" t="n">
         <v>2002</v>
@@ -5299,7 +5299,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G170" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G171" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G172" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G173" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G174" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G175" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G176" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G177" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G178" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G179" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H179" t="n">
         <v>720</v>
@@ -5589,7 +5589,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G180" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G181" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G182" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G183" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G184" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G185" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G186" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H186" t="n">
         <v>4655</v>
@@ -5792,7 +5792,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G187" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G188" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G189" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G190" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G191" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G192" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G193" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G194" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G195" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G196" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>0.284709990024567</v>
       </c>
       <c r="G197" t="n">
-        <v>0.239598244428635</v>
+        <v>0.239598229527473</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0.264829993247986</v>
       </c>
       <c r="G241" t="n">
-        <v>0.222868204116821</v>
+        <v>0.222868219017982</v>
       </c>
       <c r="H241" t="n">
         <v>996</v>
@@ -7648,7 +7648,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G251" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H251" t="n">
         <v>3503</v>
@@ -7677,7 +7677,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G252" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G253" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G254" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G255" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H255" t="n">
         <v>1200</v>
@@ -7793,7 +7793,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G256" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G257" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G258" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G259" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G260" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G261" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G262" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G263" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G264" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H264" t="n">
         <v>61267</v>
@@ -8054,7 +8054,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G265" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G266" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G267" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G268" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G269" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G270" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G271" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G272" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G273" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>0.250744998455048</v>
       </c>
       <c r="G274" t="n">
-        <v>0.211014956235886</v>
+        <v>0.211014941334724</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>0.230066001415253</v>
       </c>
       <c r="G285" t="n">
-        <v>0.193612515926361</v>
+        <v>0.1936125010252</v>
       </c>
       <c r="H285" t="n">
         <v>13013</v>
@@ -8663,7 +8663,7 @@
         <v>0.230066001415253</v>
       </c>
       <c r="G286" t="n">
-        <v>0.193612515926361</v>
+        <v>0.1936125010252</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>0.240455001592636</v>
       </c>
       <c r="G290" t="n">
-        <v>0.202355399727821</v>
+        <v>0.20235538482666</v>
       </c>
       <c r="H290" t="n">
         <v>173</v>
@@ -8808,7 +8808,7 @@
         <v>0.240455001592636</v>
       </c>
       <c r="G291" t="n">
-        <v>0.202355399727821</v>
+        <v>0.20235538482666</v>
       </c>
       <c r="H291" t="n">
         <v>2701</v>
@@ -9040,7 +9040,7 @@
         <v>0.240755006670952</v>
       </c>
       <c r="G299" t="n">
-        <v>0.202607870101929</v>
+        <v>0.202607855200768</v>
       </c>
       <c r="H299" t="n">
         <v>1701</v>
@@ -9069,7 +9069,7 @@
         <v>0.240755006670952</v>
       </c>
       <c r="G300" t="n">
-        <v>0.202607870101929</v>
+        <v>0.202607855200768</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>0.240755006670952</v>
       </c>
       <c r="G301" t="n">
-        <v>0.202607870101929</v>
+        <v>0.202607855200768</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>0.240755006670952</v>
       </c>
       <c r="G302" t="n">
-        <v>0.202607870101929</v>
+        <v>0.202607855200768</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>0.243852004408836</v>
       </c>
       <c r="G323" t="n">
-        <v>0.205214142799377</v>
+        <v>0.205214157700539</v>
       </c>
       <c r="H323" t="n">
         <v>1100</v>
@@ -9765,7 +9765,7 @@
         <v>0.243852004408836</v>
       </c>
       <c r="G324" t="n">
-        <v>0.205214142799377</v>
+        <v>0.205214157700539</v>
       </c>
       <c r="H324" t="n">
         <v>4004</v>
@@ -9823,7 +9823,7 @@
         <v>0.250445008277893</v>
       </c>
       <c r="G326" t="n">
-        <v>0.210762515664101</v>
+        <v>0.210762500762939</v>
       </c>
       <c r="H326" t="n">
         <v>1001</v>
@@ -9852,7 +9852,7 @@
         <v>0.255739986896515</v>
       </c>
       <c r="G327" t="n">
-        <v>0.215218499302864</v>
+        <v>0.215218484401703</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>0.269724994897842</v>
       </c>
       <c r="G331" t="n">
-        <v>0.226987615227699</v>
+        <v>0.22698763012886</v>
       </c>
       <c r="H331" t="n">
         <v>500</v>
@@ -9997,7 +9997,7 @@
         <v>0.269724994897842</v>
       </c>
       <c r="G332" t="n">
-        <v>0.226987615227699</v>
+        <v>0.22698763012886</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G366" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H366" t="n">
         <v>3503</v>
@@ -11012,7 +11012,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G367" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G368" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G369" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G370" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G371" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G372" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G373" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G374" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G375" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G376" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G377" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G378" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G379" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>0.299694985151291</v>
       </c>
       <c r="G380" t="n">
-        <v>0.252208918333054</v>
+        <v>0.252208888530731</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>0.324669986963272</v>
       </c>
       <c r="G397" t="n">
-        <v>0.273226708173752</v>
+        <v>0.273226678371429</v>
       </c>
       <c r="H397" t="n">
         <v>1</v>
@@ -11911,7 +11911,7 @@
         <v>0.33465901017189</v>
       </c>
       <c r="G398" t="n">
-        <v>0.281632989645004</v>
+        <v>0.281632959842682</v>
       </c>
       <c r="H398" t="n">
         <v>501</v>
@@ -11998,7 +11998,7 @@
         <v>0.347645998001099</v>
       </c>
       <c r="G401" t="n">
-        <v>0.292562186717987</v>
+        <v>0.292562216520309</v>
       </c>
       <c r="H401" t="n">
         <v>1</v>
@@ -12027,7 +12027,7 @@
         <v>0.347645998001099</v>
       </c>
       <c r="G402" t="n">
-        <v>0.292562186717987</v>
+        <v>0.292562216520309</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>0.354638993740082</v>
       </c>
       <c r="G403" t="n">
-        <v>0.298447161912918</v>
+        <v>0.298447132110596</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -12085,7 +12085,7 @@
         <v>0.354638993740082</v>
       </c>
       <c r="G404" t="n">
-        <v>0.298447161912918</v>
+        <v>0.298447132110596</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>0.354638993740082</v>
       </c>
       <c r="G405" t="n">
-        <v>0.298447161912918</v>
+        <v>0.298447132110596</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>0.383610010147095</v>
       </c>
       <c r="G410" t="n">
-        <v>0.322827756404877</v>
+        <v>0.322827786207199</v>
       </c>
       <c r="H410" t="n">
         <v>1</v>
@@ -12288,7 +12288,7 @@
         <v>0.383610010147095</v>
       </c>
       <c r="G411" t="n">
-        <v>0.322827756404877</v>
+        <v>0.322827786207199</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G552" t="n">
-        <v>0.492307990789413</v>
+        <v>0.492307901382446</v>
       </c>
       <c r="H552" t="n">
         <v>12500</v>
@@ -16406,7 +16406,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G553" t="n">
-        <v>0.492307990789413</v>
+        <v>0.492307901382446</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G554" t="n">
-        <v>0.492307990789413</v>
+        <v>0.492307901382446</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G559" t="n">
-        <v>0.673241674900055</v>
+        <v>0.67324161529541</v>
       </c>
       <c r="H559" t="n">
         <v>110992</v>
@@ -16725,7 +16725,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G564" t="n">
-        <v>0.572255313396454</v>
+        <v>0.572255373001099</v>
       </c>
       <c r="H564" t="n">
         <v>4834</v>
@@ -16986,7 +16986,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G573" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H573" t="n">
         <v>6100</v>
@@ -17015,7 +17015,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G574" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G575" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H575" t="n">
         <v>25787</v>
@@ -17392,7 +17392,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G587" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H587" t="n">
         <v>5075</v>
@@ -17421,7 +17421,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G588" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G589" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.492307990789413</v>
+        <v>0.492307901382446</v>
       </c>
       <c r="H590" t="n">
         <v>6921</v>
@@ -17537,7 +17537,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G592" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H592" t="n">
         <v>517</v>
@@ -17566,7 +17566,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G593" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G594" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G595" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G596" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G603" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H603" t="n">
         <v>3100</v>
@@ -17885,7 +17885,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G604" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G605" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H614" t="n">
         <v>100</v>
@@ -18204,7 +18204,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G615" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G626" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H626" t="n">
         <v>2107</v>
@@ -19045,7 +19045,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G644" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H644" t="n">
         <v>6400</v>
@@ -19074,7 +19074,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G645" t="n">
-        <v>0.492307990789413</v>
+        <v>0.492307901382446</v>
       </c>
       <c r="H645" t="n">
         <v>777</v>
@@ -19132,7 +19132,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G647" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H647" t="n">
         <v>2500</v>
@@ -19161,7 +19161,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G648" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H648" t="n">
         <v>7047</v>
@@ -19190,7 +19190,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G649" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -19422,7 +19422,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G657" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H657" t="n">
         <v>17751</v>
@@ -19451,7 +19451,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G658" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H658" t="n">
         <v>1000</v>
@@ -19480,7 +19480,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G659" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H659" t="n">
         <v>129</v>
@@ -19509,7 +19509,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G660" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H660" t="n">
         <v>48</v>
@@ -19538,7 +19538,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G661" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H661" t="n">
         <v>48</v>
@@ -20379,7 +20379,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G690" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H690" t="n">
         <v>1820</v>
@@ -20408,7 +20408,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G691" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G692" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G693" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G694" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H694" t="n">
         <v>960</v>
@@ -20524,7 +20524,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G695" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G696" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G697" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -20611,7 +20611,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G698" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G699" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G705" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H705" t="n">
         <v>58</v>
@@ -20843,7 +20843,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G706" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G707" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G708" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G709" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G710" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G711" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H711" t="n">
         <v>11001</v>
@@ -21017,7 +21017,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G712" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H712" t="n">
         <v>12400</v>
@@ -21307,7 +21307,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G722" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H722" t="n">
         <v>44120</v>
@@ -21423,7 +21423,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G726" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H726" t="n">
         <v>1485</v>
@@ -21452,7 +21452,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H727" t="n">
         <v>4004</v>
@@ -21481,7 +21481,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H728" t="n">
         <v>2574</v>
@@ -21510,7 +21510,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G729" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H729" t="n">
         <v>10270</v>
@@ -21539,7 +21539,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G730" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H730" t="n">
         <v>481</v>
@@ -21597,7 +21597,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G732" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H732" t="n">
         <v>390</v>
@@ -21626,7 +21626,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G733" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G734" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H734" t="n">
         <v>50</v>
@@ -21974,7 +21974,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G745" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H745" t="n">
         <v>100</v>
@@ -22003,7 +22003,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -22032,7 +22032,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H747" t="n">
         <v>17911</v>
@@ -22264,7 +22264,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G755" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H755" t="n">
         <v>12094</v>
@@ -22293,7 +22293,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G756" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G758" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H758" t="n">
         <v>2001</v>
@@ -22380,7 +22380,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G759" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G760" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G761" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G768" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H768" t="n">
         <v>3000</v>
@@ -22670,7 +22670,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G769" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H769" t="n">
         <v>200</v>
@@ -22699,7 +22699,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G770" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G771" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G772" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G773" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H773" t="n">
         <v>150</v>
@@ -22815,7 +22815,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G774" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G775" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G776" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H776" t="n">
         <v>2100</v>
@@ -22902,7 +22902,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G777" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H777" t="n">
         <v>11000</v>
@@ -23105,7 +23105,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H784" t="n">
         <v>1000</v>
@@ -23221,7 +23221,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G788" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H788" t="n">
         <v>1200</v>
@@ -23250,7 +23250,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G789" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H789" t="n">
         <v>1810</v>
@@ -23830,7 +23830,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G809" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H809" t="n">
         <v>30422</v>
@@ -24004,7 +24004,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G815" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H815" t="n">
         <v>4063</v>
@@ -24033,7 +24033,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G816" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -24062,7 +24062,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G817" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H817" t="n">
         <v>0</v>
@@ -24091,7 +24091,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G818" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H818" t="n">
         <v>11440</v>
@@ -24149,7 +24149,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G820" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H820" t="n">
         <v>21955</v>
@@ -24236,7 +24236,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G823" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H823" t="n">
         <v>27817</v>
@@ -24497,7 +24497,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G832" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H832" t="n">
         <v>6299</v>
@@ -24526,7 +24526,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G833" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H833" t="n">
         <v>6000</v>
@@ -24555,7 +24555,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G834" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24729,7 +24729,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G840" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H840" t="n">
         <v>3818</v>
@@ -25106,7 +25106,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G853" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H853" t="n">
         <v>20</v>
@@ -25135,7 +25135,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G854" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H854" t="n">
         <v>2000</v>
@@ -25164,7 +25164,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G855" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -25222,7 +25222,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G857" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H857" t="n">
         <v>6059</v>
@@ -25251,7 +25251,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G858" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H858" t="n">
         <v>4145</v>
@@ -25425,7 +25425,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G864" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H864" t="n">
         <v>5</v>
@@ -25454,7 +25454,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G865" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -25483,7 +25483,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G866" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H866" t="n">
         <v>2550</v>
@@ -25512,7 +25512,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G867" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25599,7 +25599,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G870" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H870" t="n">
         <v>20</v>
@@ -25628,7 +25628,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G871" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G872" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G873" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G874" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G875" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -25773,7 +25773,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G876" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G877" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G878" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G879" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G880" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -25918,7 +25918,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G881" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -25947,7 +25947,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G882" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H882" t="n">
         <v>1420</v>
@@ -25976,7 +25976,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G883" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G884" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26034,7 +26034,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G885" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -26179,7 +26179,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H890" t="n">
         <v>1052</v>
@@ -26585,7 +26585,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G904" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H904" t="n">
         <v>6495</v>
@@ -26643,7 +26643,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G906" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H906" t="n">
         <v>19728</v>
@@ -26672,7 +26672,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G907" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H907" t="n">
         <v>3367</v>
@@ -26701,7 +26701,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G908" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G911" t="n">
-        <v>0.405628085136414</v>
+        <v>0.405628055334091</v>
       </c>
       <c r="H911" t="n">
         <v>4023</v>
@@ -26817,7 +26817,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G912" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H912" t="n">
         <v>300</v>
@@ -27049,7 +27049,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H920" t="n">
         <v>3640</v>
@@ -27078,7 +27078,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G921" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G929" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H929" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G932" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H932" t="n">
         <v>6754</v>
@@ -27426,7 +27426,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G933" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -28093,7 +28093,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G956" t="n">
-        <v>0.400578767061234</v>
+        <v>0.400578796863556</v>
       </c>
       <c r="H956" t="n">
         <v>21697</v>
@@ -28122,7 +28122,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G957" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H957" t="n">
         <v>18297</v>
@@ -28151,7 +28151,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G958" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H958" t="n">
         <v>13283</v>
@@ -28180,7 +28180,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G959" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H959" t="n">
         <v>1919</v>
@@ -28499,7 +28499,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G970" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H970" t="n">
         <v>2042</v>
@@ -28528,7 +28528,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G971" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H971" t="n">
         <v>1442</v>
@@ -28673,7 +28673,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G976" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H976" t="n">
         <v>3621</v>
@@ -28702,7 +28702,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G977" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H977" t="n">
         <v>21</v>
@@ -28818,7 +28818,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G981" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H981" t="n">
         <v>946</v>
@@ -28847,7 +28847,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G982" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H982" t="n">
         <v>12589</v>
@@ -28876,7 +28876,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G983" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28905,7 +28905,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G984" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H984" t="n">
         <v>7067</v>
@@ -28992,7 +28992,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G987" t="n">
-        <v>0.395529448986053</v>
+        <v>0.395529478788376</v>
       </c>
       <c r="H987" t="n">
         <v>1370</v>
@@ -29021,7 +29021,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G988" t="n">
-        <v>0.405628085136414</v>
+        <v>0.405628055334091</v>
       </c>
       <c r="H988" t="n">
         <v>10842</v>
@@ -29079,7 +29079,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G990" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H990" t="n">
         <v>4493</v>
@@ -29137,7 +29137,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G992" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H992" t="n">
         <v>728</v>
@@ -29166,7 +29166,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G993" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H993" t="n">
         <v>99</v>
@@ -29311,7 +29311,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G998" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H998" t="n">
         <v>10198</v>
@@ -29340,7 +29340,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G999" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H1011" t="n">
         <v>8542</v>
@@ -29717,7 +29717,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H1013" t="n">
         <v>76149</v>
@@ -29775,7 +29775,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1014" t="n">
         <v>128258</v>
@@ -29833,7 +29833,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1016" t="n">
         <v>129111</v>
@@ -29862,7 +29862,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H1017" t="n">
         <v>26000</v>
@@ -29891,7 +29891,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.408994287252426</v>
+        <v>0.408994317054749</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H1019" t="n">
         <v>34275</v>
@@ -30036,7 +30036,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H1023" t="n">
         <v>31081</v>
@@ -30065,7 +30065,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1024" t="n">
         <v>56650</v>
@@ -30123,7 +30123,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1026" t="n">
         <v>300344</v>
@@ -30152,7 +30152,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H1027" t="n">
         <v>225035</v>
@@ -30181,7 +30181,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1028" t="n">
         <v>78118</v>
@@ -30239,7 +30239,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H1030" t="n">
         <v>315623</v>
@@ -30268,7 +30268,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1031" t="n">
         <v>445386</v>
@@ -30297,7 +30297,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1032" t="n">
         <v>185716</v>
@@ -30355,7 +30355,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1034" t="n">
         <v>10100</v>
@@ -30384,7 +30384,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1035" t="n">
         <v>85860</v>
@@ -30616,7 +30616,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1043" t="n">
         <v>34141</v>
@@ -30674,7 +30674,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H1045" t="n">
         <v>73650</v>
@@ -30761,7 +30761,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.441814839839935</v>
+        <v>0.441814810037613</v>
       </c>
       <c r="H1048" t="n">
         <v>185923</v>
@@ -30877,7 +30877,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1052" t="n">
         <v>171436</v>
@@ -30906,7 +30906,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.405628085136414</v>
+        <v>0.405628055334091</v>
       </c>
       <c r="H1053" t="n">
         <v>191129</v>
@@ -30935,7 +30935,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1054" t="n">
         <v>15804</v>
@@ -30964,7 +30964,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1055" t="n">
         <v>22070</v>
@@ -30993,7 +30993,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1056" t="n">
         <v>12681</v>
@@ -31022,7 +31022,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.400578767061234</v>
+        <v>0.400578796863556</v>
       </c>
       <c r="H1057" t="n">
         <v>13092</v>
@@ -31138,7 +31138,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1061" t="n">
         <v>2600</v>
@@ -31196,7 +31196,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.323156028985977</v>
+        <v>0.323155969381332</v>
       </c>
       <c r="H1063" t="n">
         <v>32766</v>
@@ -31254,7 +31254,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.336620837450027</v>
+        <v>0.336620807647705</v>
       </c>
       <c r="H1065" t="n">
         <v>2700</v>
@@ -31283,7 +31283,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.336620837450027</v>
+        <v>0.336620807647705</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -31718,7 +31718,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.336620837450027</v>
+        <v>0.336620807647705</v>
       </c>
       <c r="H1081" t="n">
         <v>102477</v>
@@ -31776,7 +31776,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.336620837450027</v>
+        <v>0.336620807647705</v>
       </c>
       <c r="H1083" t="n">
         <v>14682</v>
@@ -31805,7 +31805,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.336620837450027</v>
+        <v>0.336620807647705</v>
       </c>
       <c r="H1084" t="n">
         <v>286185</v>
@@ -31921,7 +31921,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1088" t="n">
         <v>33000</v>
@@ -32037,7 +32037,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1092" t="n">
         <v>173326</v>
@@ -32211,7 +32211,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1098" t="n">
         <v>186861</v>
@@ -32240,7 +32240,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1099" t="n">
         <v>48976</v>
@@ -32356,7 +32356,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1103" t="n">
         <v>1000</v>
@@ -32385,7 +32385,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1104" t="n">
         <v>13324</v>
@@ -32472,7 +32472,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.323156028985977</v>
+        <v>0.323155969381332</v>
       </c>
       <c r="H1107" t="n">
         <v>6104</v>
@@ -32559,7 +32559,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.331571489572525</v>
+        <v>0.331571459770203</v>
       </c>
       <c r="H1110" t="n">
         <v>43298</v>
@@ -32675,7 +32675,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.323156028985977</v>
+        <v>0.323155969381332</v>
       </c>
       <c r="H1114" t="n">
         <v>32456</v>
@@ -32994,7 +32994,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1125" t="n">
         <v>20187</v>
@@ -33023,7 +33023,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1126" t="n">
         <v>111003</v>
@@ -33255,7 +33255,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.388797014951706</v>
+        <v>0.388797044754028</v>
       </c>
       <c r="H1134" t="n">
         <v>4000</v>
@@ -33371,7 +33371,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1138" t="n">
         <v>5015</v>
@@ -33400,7 +33400,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1139" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1140" t="n">
         <v>0</v>
@@ -33458,7 +33458,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1141" t="n">
         <v>0</v>
@@ -33487,7 +33487,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1142" t="n">
         <v>16383</v>
@@ -33545,7 +33545,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1144" t="n">
         <v>6000</v>
@@ -33603,7 +33603,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1146" t="n">
         <v>1000</v>
@@ -33632,7 +33632,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1147" t="n">
         <v>200</v>
@@ -33661,7 +33661,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.370282888412476</v>
+        <v>0.370282918214798</v>
       </c>
       <c r="H1148" t="n">
         <v>850</v>
@@ -33777,7 +33777,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.370282888412476</v>
+        <v>0.370282918214798</v>
       </c>
       <c r="H1152" t="n">
         <v>12599</v>
@@ -33864,7 +33864,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.385430812835693</v>
+        <v>0.385430842638016</v>
       </c>
       <c r="H1155" t="n">
         <v>7348</v>
@@ -33951,7 +33951,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1158" t="n">
         <v>16090</v>
@@ -33980,7 +33980,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1159" t="n">
         <v>4444</v>
@@ -34009,7 +34009,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1160" t="n">
         <v>1200</v>
@@ -34038,7 +34038,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1161" t="n">
         <v>0</v>
@@ -34096,7 +34096,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1163" t="n">
         <v>14416</v>
@@ -34125,7 +34125,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1164" t="n">
         <v>1372</v>
@@ -34154,7 +34154,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.385430812835693</v>
+        <v>0.385430842638016</v>
       </c>
       <c r="H1165" t="n">
         <v>100</v>
@@ -34183,7 +34183,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.387113928794861</v>
+        <v>0.387113958597183</v>
       </c>
       <c r="H1166" t="n">
         <v>5366</v>
@@ -34212,7 +34212,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1167" t="n">
         <v>40500</v>
@@ -34241,7 +34241,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1168" t="n">
         <v>80018</v>
@@ -34270,7 +34270,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1170" t="n">
         <v>1000</v>
@@ -34328,7 +34328,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34357,7 +34357,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.370282888412476</v>
+        <v>0.370282918214798</v>
       </c>
       <c r="H1172" t="n">
         <v>12686</v>
@@ -34386,7 +34386,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1173" t="n">
         <v>999</v>
@@ -34415,7 +34415,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.378698408603668</v>
+        <v>0.378698438405991</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.365233540534973</v>
+        <v>0.365233570337296</v>
       </c>
       <c r="H1175" t="n">
         <v>37354</v>
@@ -34531,7 +34531,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.375332176685333</v>
+        <v>0.375332206487656</v>
       </c>
       <c r="H1178" t="n">
         <v>100</v>
@@ -34821,7 +34821,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1188" t="n">
         <v>22528</v>
@@ -34937,7 +34937,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1192" t="n">
         <v>121882</v>
@@ -34966,7 +34966,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1193" t="n">
         <v>43996</v>
@@ -34995,7 +34995,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1194" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.402261883020401</v>
+        <v>0.402261853218079</v>
       </c>
       <c r="H1202" t="n">
         <v>27800</v>
@@ -35285,7 +35285,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.405628085136414</v>
+        <v>0.405628055334091</v>
       </c>
       <c r="H1204" t="n">
         <v>23702</v>
@@ -35314,7 +35314,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1205" t="n">
         <v>196839</v>
@@ -35343,7 +35343,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1206" t="n">
         <v>19162</v>
@@ -35430,7 +35430,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1209" t="n">
         <v>108673</v>
@@ -35633,7 +35633,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1216" t="n">
         <v>4866</v>
@@ -35662,7 +35662,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1217" t="n">
         <v>31520</v>
@@ -35691,7 +35691,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1218" t="n">
         <v>124593</v>
@@ -35720,7 +35720,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.415726721286774</v>
+        <v>0.415726691484451</v>
       </c>
       <c r="H1219" t="n">
         <v>0</v>
@@ -35778,7 +35778,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H1221" t="n">
         <v>43150</v>
@@ -35807,7 +35807,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1222" t="n">
         <v>32</v>
@@ -35923,7 +35923,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.403944939374924</v>
+        <v>0.403944969177246</v>
       </c>
       <c r="H1226" t="n">
         <v>147498</v>
@@ -35981,7 +35981,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.405628085136414</v>
+        <v>0.405628055334091</v>
       </c>
       <c r="H1228" t="n">
         <v>7300</v>
@@ -36039,7 +36039,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1230" t="n">
         <v>80720</v>
@@ -36068,7 +36068,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H1231" t="n">
         <v>400</v>
@@ -36097,7 +36097,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H1232" t="n">
         <v>0</v>
@@ -36126,7 +36126,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.414043605327606</v>
+        <v>0.414043575525284</v>
       </c>
       <c r="H1233" t="n">
         <v>0</v>
@@ -36300,7 +36300,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1239" t="n">
         <v>10855</v>
@@ -36474,7 +36474,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.419092893600464</v>
+        <v>0.419092863798141</v>
       </c>
       <c r="H1245" t="n">
         <v>34598</v>
@@ -36532,7 +36532,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.424983769655228</v>
+        <v>0.424983739852905</v>
       </c>
       <c r="H1247" t="n">
         <v>67956</v>
@@ -36822,7 +36822,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H1257" t="n">
         <v>150427</v>
@@ -36909,7 +36909,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.450230360031128</v>
+        <v>0.45023038983345</v>
       </c>
       <c r="H1260" t="n">
         <v>56414</v>
@@ -36938,7 +36938,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H1261" t="n">
         <v>18900</v>
@@ -36996,7 +36996,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H1263" t="n">
         <v>225009</v>
@@ -37054,7 +37054,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1265" t="n">
         <v>180594</v>
@@ -37083,7 +37083,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.559632062911987</v>
+        <v>0.559632122516632</v>
       </c>
       <c r="H1266" t="n">
         <v>109892</v>
@@ -37112,7 +37112,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.572255313396454</v>
+        <v>0.572255373001099</v>
       </c>
       <c r="H1267" t="n">
         <v>62883</v>
@@ -37141,7 +37141,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.559632062911987</v>
+        <v>0.559632122516632</v>
       </c>
       <c r="H1268" t="n">
         <v>39432</v>
@@ -37170,7 +37170,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.559632062911987</v>
+        <v>0.559632122516632</v>
       </c>
       <c r="H1269" t="n">
         <v>31720</v>
@@ -37199,7 +37199,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.559632062911987</v>
+        <v>0.559632122516632</v>
       </c>
       <c r="H1270" t="n">
         <v>81707</v>
@@ -37286,7 +37286,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1273" t="n">
         <v>28609</v>
@@ -37315,7 +37315,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1274" t="n">
         <v>130291</v>
@@ -37344,7 +37344,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.551216602325439</v>
+        <v>0.551216542720795</v>
       </c>
       <c r="H1275" t="n">
         <v>20833</v>
@@ -37402,7 +37402,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1277" t="n">
         <v>25653</v>
@@ -37547,7 +37547,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H1282" t="n">
         <v>39031</v>
@@ -37576,7 +37576,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1283" t="n">
         <v>43510</v>
@@ -37634,7 +37634,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1285" t="n">
         <v>194918</v>
@@ -37663,7 +37663,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H1286" t="n">
         <v>230961</v>
@@ -37721,7 +37721,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1288" t="n">
         <v>122935</v>
@@ -37750,7 +37750,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1289" t="n">
         <v>152115</v>
@@ -37779,7 +37779,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1290" t="n">
         <v>0</v>
@@ -37808,7 +37808,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.500723421573639</v>
+        <v>0.500723481178284</v>
       </c>
       <c r="H1291" t="n">
         <v>31819</v>
@@ -38011,7 +38011,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1298" t="n">
         <v>156143</v>
@@ -38156,7 +38156,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1303" t="n">
         <v>31468</v>
@@ -38272,7 +38272,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1307" t="n">
         <v>38734</v>
@@ -38301,7 +38301,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H1308" t="n">
         <v>5665</v>
@@ -38330,7 +38330,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1309" t="n">
         <v>189642</v>
@@ -38388,7 +38388,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1311" t="n">
         <v>153824</v>
@@ -38417,7 +38417,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1312" t="n">
         <v>26300</v>
@@ -38446,7 +38446,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1313" t="n">
         <v>34809</v>
@@ -38475,7 +38475,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H1314" t="n">
         <v>46344</v>
@@ -38504,7 +38504,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1315" t="n">
         <v>48389</v>
@@ -38533,7 +38533,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1316" t="n">
         <v>1802</v>
@@ -38562,7 +38562,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1317" t="n">
         <v>14721</v>
@@ -38620,7 +38620,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1319" t="n">
         <v>86177</v>
@@ -38649,7 +38649,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1320" t="n">
         <v>0</v>
@@ -38678,7 +38678,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1321" t="n">
         <v>33204</v>
@@ -38707,7 +38707,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H1322" t="n">
         <v>30807</v>
@@ -38823,7 +38823,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.458645850419998</v>
+        <v>0.458645880222321</v>
       </c>
       <c r="H1326" t="n">
         <v>30912</v>
@@ -38939,7 +38939,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.475476861000061</v>
+        <v>0.475476831197739</v>
       </c>
       <c r="H1330" t="n">
         <v>21800</v>
@@ -38968,7 +38968,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.483892440795898</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="H1331" t="n">
         <v>100008</v>
@@ -39026,7 +39026,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H1333" t="n">
         <v>14634</v>
@@ -39055,7 +39055,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.489783227443695</v>
+        <v>0.489783257246017</v>
       </c>
       <c r="H1334" t="n">
         <v>235642</v>
@@ -39084,7 +39084,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.47968465089798</v>
+        <v>0.479684621095657</v>
       </c>
       <c r="H1335" t="n">
         <v>61586</v>
@@ -39113,7 +39113,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.484733909368515</v>
+        <v>0.484733939170837</v>
       </c>
       <c r="H1336" t="n">
         <v>35851</v>
@@ -39171,7 +39171,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.471269130706787</v>
+        <v>0.471269160509109</v>
       </c>
       <c r="H1338" t="n">
         <v>15249</v>
@@ -39258,7 +39258,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.49483260512352</v>
+        <v>0.494832575321198</v>
       </c>
       <c r="H1341" t="n">
         <v>47730</v>
@@ -39345,7 +39345,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.553741157054901</v>
+        <v>0.553741216659546</v>
       </c>
       <c r="H1344" t="n">
         <v>333371</v>
@@ -39374,7 +39374,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H1345" t="n">
         <v>221281</v>
@@ -39548,7 +39548,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1351" t="n">
         <v>314919</v>
@@ -39606,7 +39606,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.525128424167633</v>
+        <v>0.525128483772278</v>
       </c>
       <c r="H1353" t="n">
         <v>54021</v>
@@ -39780,7 +39780,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H1359" t="n">
         <v>7550</v>
@@ -39809,7 +39809,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.49483260512352</v>
+        <v>0.494832575321198</v>
       </c>
       <c r="H1360" t="n">
         <v>31550</v>
@@ -39896,7 +39896,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.50324809551239</v>
+        <v>0.503248035907745</v>
       </c>
       <c r="H1363" t="n">
         <v>88422</v>
@@ -39925,7 +39925,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.504931151866913</v>
+        <v>0.504931211471558</v>
       </c>
       <c r="H1364" t="n">
         <v>73200</v>
@@ -39954,7 +39954,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.508297443389893</v>
+        <v>0.508297383785248</v>
       </c>
       <c r="H1365" t="n">
         <v>77247</v>
@@ -40128,7 +40128,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.49314945936203</v>
+        <v>0.493149518966675</v>
       </c>
       <c r="H1371" t="n">
         <v>11398</v>
@@ -40157,7 +40157,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.50324809551239</v>
+        <v>0.503248035907745</v>
       </c>
       <c r="H1372" t="n">
         <v>68646</v>
@@ -40302,7 +40302,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.515029847621918</v>
+        <v>0.515029907226562</v>
       </c>
       <c r="H1377" t="n">
         <v>1834314</v>
@@ -40331,7 +40331,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1378" t="n">
         <v>1693418</v>
@@ -40360,7 +40360,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.560473620891571</v>
+        <v>0.560473680496216</v>
       </c>
       <c r="H1379" t="n">
         <v>1780476</v>
@@ -40505,7 +40505,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.560473620891571</v>
+        <v>0.560473680496216</v>
       </c>
       <c r="H1384" t="n">
         <v>697633</v>
@@ -40592,7 +40592,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.547008812427521</v>
+        <v>0.547008752822876</v>
       </c>
       <c r="H1387" t="n">
         <v>131787</v>
@@ -40650,7 +40650,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.531860888004303</v>
+        <v>0.531860947608948</v>
       </c>
       <c r="H1389" t="n">
         <v>76445</v>
@@ -40737,7 +40737,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1392" t="n">
         <v>71368</v>
@@ -40766,7 +40766,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1393" t="n">
         <v>58543</v>
@@ -40940,7 +40940,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.53017783164978</v>
+        <v>0.530177772045135</v>
       </c>
       <c r="H1399" t="n">
         <v>10500</v>
@@ -40969,7 +40969,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.525128424167633</v>
+        <v>0.525128483772278</v>
       </c>
       <c r="H1400" t="n">
         <v>37000</v>
@@ -41027,7 +41027,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.508297443389893</v>
+        <v>0.508297383785248</v>
       </c>
       <c r="H1402" t="n">
         <v>147855</v>
@@ -41056,7 +41056,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.515029847621918</v>
+        <v>0.515029907226562</v>
       </c>
       <c r="H1403" t="n">
         <v>18271</v>
@@ -41288,7 +41288,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1411" t="n">
         <v>179815</v>
@@ -41346,7 +41346,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.531860888004303</v>
+        <v>0.531860947608948</v>
       </c>
       <c r="H1413" t="n">
         <v>17843</v>
@@ -41404,7 +41404,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.531860888004303</v>
+        <v>0.531860947608948</v>
       </c>
       <c r="H1415" t="n">
         <v>210032</v>
@@ -41462,7 +41462,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1417" t="n">
         <v>129113</v>
@@ -41491,7 +41491,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.533543944358826</v>
+        <v>0.53354400396347</v>
       </c>
       <c r="H1418" t="n">
         <v>143063</v>
@@ -41578,7 +41578,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1421" t="n">
         <v>20596</v>
@@ -41607,7 +41607,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1422" t="n">
         <v>0</v>
@@ -41636,7 +41636,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1423" t="n">
         <v>12700</v>
@@ -41752,7 +41752,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1427" t="n">
         <v>22589</v>
@@ -41839,7 +41839,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.526592254638672</v>
+        <v>0.526592314243317</v>
       </c>
       <c r="H1430" t="n">
         <v>57670</v>
@@ -42042,7 +42042,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.545709490776062</v>
+        <v>0.545709550380707</v>
       </c>
       <c r="H1437" t="n">
         <v>420828</v>
@@ -42071,7 +42071,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.545709490776062</v>
+        <v>0.545709550380707</v>
       </c>
       <c r="H1438" t="n">
         <v>245936</v>
@@ -42187,7 +42187,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.545709490776062</v>
+        <v>0.545709550380707</v>
       </c>
       <c r="H1442" t="n">
         <v>41421</v>
@@ -42245,7 +42245,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.554399132728577</v>
+        <v>0.554399192333221</v>
       </c>
       <c r="H1444" t="n">
         <v>91300</v>
@@ -42274,7 +42274,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.554399132728577</v>
+        <v>0.554399192333221</v>
       </c>
       <c r="H1445" t="n">
         <v>8389</v>
@@ -42303,7 +42303,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.554399132728577</v>
+        <v>0.554399192333221</v>
       </c>
       <c r="H1446" t="n">
         <v>8600</v>
@@ -42361,7 +42361,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.545709490776062</v>
+        <v>0.545709550380707</v>
       </c>
       <c r="H1448" t="n">
         <v>56857</v>
@@ -42448,7 +42448,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1451" t="n">
         <v>53400</v>
@@ -42593,7 +42593,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1456" t="n">
         <v>40188</v>
@@ -42622,7 +42622,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1457" t="n">
         <v>23825</v>
@@ -42883,7 +42883,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1466" t="n">
         <v>96407</v>
@@ -42970,7 +42970,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1469" t="n">
         <v>2000</v>
@@ -43086,7 +43086,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1473" t="n">
         <v>31803</v>
@@ -43115,7 +43115,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1474" t="n">
         <v>10200</v>
@@ -43144,7 +43144,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1475" t="n">
         <v>7117</v>
@@ -43173,7 +43173,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1476" t="n">
         <v>8000</v>
@@ -43202,7 +43202,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1477" t="n">
         <v>18470</v>
@@ -43231,7 +43231,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1478" t="n">
         <v>1415</v>
@@ -43347,7 +43347,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.545709490776062</v>
+        <v>0.545709550380707</v>
       </c>
       <c r="H1482" t="n">
         <v>45900</v>
@@ -43376,7 +43376,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1483" t="n">
         <v>20600</v>
@@ -43405,7 +43405,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1484" t="n">
         <v>97254</v>
@@ -43579,7 +43579,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1490" t="n">
         <v>85442</v>
@@ -43608,7 +43608,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1491" t="n">
         <v>68594</v>
@@ -43695,7 +43695,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1494" t="n">
         <v>120180</v>
@@ -43724,7 +43724,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.53354400396347</v>
+        <v>0.533544063568115</v>
       </c>
       <c r="H1495" t="n">
         <v>56466</v>
@@ -43927,7 +43927,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1502" t="n">
         <v>130100</v>
@@ -43985,7 +43985,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.493571668863297</v>
+        <v>0.493571698665619</v>
       </c>
       <c r="H1504" t="n">
         <v>58208</v>
@@ -44072,7 +44072,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.524854362010956</v>
+        <v>0.524854302406311</v>
       </c>
       <c r="H1507" t="n">
         <v>36890</v>
@@ -44159,7 +44159,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1510" t="n">
         <v>75470</v>
@@ -44217,7 +44217,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.526592254638672</v>
+        <v>0.526592314243317</v>
       </c>
       <c r="H1512" t="n">
         <v>32050</v>
@@ -44246,7 +44246,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1513" t="n">
         <v>62515</v>
@@ -44333,7 +44333,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.519640564918518</v>
+        <v>0.519640505313873</v>
       </c>
       <c r="H1516" t="n">
         <v>11000</v>
@@ -44362,7 +44362,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1517" t="n">
         <v>1500</v>
@@ -44420,7 +44420,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1519" t="n">
         <v>3844</v>
@@ -44478,7 +44478,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1521" t="n">
         <v>22034</v>
@@ -44507,7 +44507,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1522" t="n">
         <v>33543</v>
@@ -44536,7 +44536,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1523" t="n">
         <v>20500</v>
@@ -44565,7 +44565,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1524" t="n">
         <v>21122</v>
@@ -44594,7 +44594,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.521378457546234</v>
+        <v>0.521378517150879</v>
       </c>
       <c r="H1525" t="n">
         <v>39172</v>
@@ -44652,7 +44652,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.608274877071381</v>
+        <v>0.608274936676025</v>
       </c>
       <c r="H1527" t="n">
         <v>1923150</v>
@@ -44768,7 +44768,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.590895593166351</v>
+        <v>0.590895652770996</v>
       </c>
       <c r="H1531" t="n">
         <v>228957</v>
@@ -44797,7 +44797,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.594371497631073</v>
+        <v>0.594371557235718</v>
       </c>
       <c r="H1532" t="n">
         <v>202785</v>
@@ -45029,7 +45029,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.667364537715912</v>
+        <v>0.667364478111267</v>
       </c>
       <c r="H1540" t="n">
         <v>1687318</v>
@@ -45087,7 +45087,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.603061079978943</v>
+        <v>0.603061139583588</v>
       </c>
       <c r="H1542" t="n">
         <v>992729</v>
@@ -45174,7 +45174,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1545" t="n">
         <v>62569</v>
@@ -45203,7 +45203,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.632605910301208</v>
+        <v>0.632605850696564</v>
       </c>
       <c r="H1546" t="n">
         <v>296852</v>
@@ -45319,7 +45319,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.6447713971138</v>
+        <v>0.644771337509155</v>
       </c>
       <c r="H1550" t="n">
         <v>78046</v>
@@ -45377,7 +45377,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.625654220581055</v>
+        <v>0.62565416097641</v>
       </c>
       <c r="H1552" t="n">
         <v>118694</v>
@@ -45406,7 +45406,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.620440423488617</v>
+        <v>0.620440363883972</v>
       </c>
       <c r="H1553" t="n">
         <v>40138</v>
@@ -45435,7 +45435,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.6447713971138</v>
+        <v>0.644771337509155</v>
       </c>
       <c r="H1554" t="n">
         <v>168777</v>
@@ -45464,7 +45464,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.637819707393646</v>
+        <v>0.637819647789001</v>
       </c>
       <c r="H1555" t="n">
         <v>144540</v>
@@ -45493,7 +45493,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.643033504486084</v>
+        <v>0.643033444881439</v>
       </c>
       <c r="H1556" t="n">
         <v>34141</v>
@@ -45522,7 +45522,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.632605910301208</v>
+        <v>0.632605850696564</v>
       </c>
       <c r="H1557" t="n">
         <v>187668</v>
@@ -45551,7 +45551,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.622178375720978</v>
+        <v>0.622178316116333</v>
       </c>
       <c r="H1558" t="n">
         <v>259787</v>
@@ -45580,7 +45580,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1559" t="n">
         <v>145055</v>
@@ -45609,7 +45609,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.608274877071381</v>
+        <v>0.608274936676025</v>
       </c>
       <c r="H1560" t="n">
         <v>146480</v>
@@ -45638,7 +45638,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.603061079978943</v>
+        <v>0.603061139583588</v>
       </c>
       <c r="H1561" t="n">
         <v>126966</v>
@@ -45667,7 +45667,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.610012888908386</v>
+        <v>0.610012829303741</v>
       </c>
       <c r="H1562" t="n">
         <v>157798</v>
@@ -45725,7 +45725,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.608274877071381</v>
+        <v>0.608274936676025</v>
       </c>
       <c r="H1564" t="n">
         <v>257935</v>
@@ -45754,7 +45754,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.583943843841553</v>
+        <v>0.583943903446198</v>
       </c>
       <c r="H1565" t="n">
         <v>431015</v>
@@ -45841,7 +45841,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.571778357028961</v>
+        <v>0.571778416633606</v>
       </c>
       <c r="H1568" t="n">
         <v>104617</v>
@@ -45928,7 +45928,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.538757741451263</v>
+        <v>0.538757801055908</v>
       </c>
       <c r="H1571" t="n">
         <v>391532</v>
@@ -45986,7 +45986,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.519640564918518</v>
+        <v>0.519640505313873</v>
       </c>
       <c r="H1573" t="n">
         <v>80876</v>
@@ -46131,7 +46131,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.557874977588654</v>
+        <v>0.557875037193298</v>
       </c>
       <c r="H1578" t="n">
         <v>33904</v>
@@ -46189,7 +46189,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.571778357028961</v>
+        <v>0.571778416633606</v>
       </c>
       <c r="H1580" t="n">
         <v>367235</v>
@@ -46276,7 +46276,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.596109390258789</v>
+        <v>0.596109449863434</v>
       </c>
       <c r="H1583" t="n">
         <v>95238</v>
@@ -46421,7 +46421,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985134601593</v>
       </c>
       <c r="H1588" t="n">
         <v>352682</v>
@@ -46537,7 +46537,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.68300586938858</v>
+        <v>0.683005809783936</v>
       </c>
       <c r="H1592" t="n">
         <v>1028370</v>
@@ -46682,7 +46682,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.662150740623474</v>
+        <v>0.662150681018829</v>
       </c>
       <c r="H1597" t="n">
         <v>316152</v>
@@ -46827,7 +46827,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985134601593</v>
       </c>
       <c r="H1602" t="n">
         <v>310236</v>
@@ -46856,7 +46856,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.649985194206238</v>
+        <v>0.649985134601593</v>
       </c>
       <c r="H1603" t="n">
         <v>205158</v>
@@ -46943,7 +46943,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.643033504486084</v>
+        <v>0.643033444881439</v>
       </c>
       <c r="H1606" t="n">
         <v>88422</v>
@@ -46972,7 +46972,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.643033504486084</v>
+        <v>0.643033444881439</v>
       </c>
       <c r="H1607" t="n">
         <v>111714</v>
@@ -47117,7 +47117,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.6447713971138</v>
+        <v>0.644771337509155</v>
       </c>
       <c r="H1612" t="n">
         <v>98209</v>
@@ -47146,7 +47146,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.625654220581055</v>
+        <v>0.62565416097641</v>
       </c>
       <c r="H1613" t="n">
         <v>68532</v>
@@ -47175,7 +47175,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.637819707393646</v>
+        <v>0.637819647789001</v>
       </c>
       <c r="H1614" t="n">
         <v>136673</v>
@@ -47233,7 +47233,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.608274877071381</v>
+        <v>0.608274936676025</v>
       </c>
       <c r="H1616" t="n">
         <v>121705</v>
@@ -47262,7 +47262,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.620440423488617</v>
+        <v>0.620440363883972</v>
       </c>
       <c r="H1617" t="n">
         <v>60877</v>
@@ -47320,7 +47320,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.618702530860901</v>
+        <v>0.618702471256256</v>
       </c>
       <c r="H1619" t="n">
         <v>15500</v>
@@ -47349,7 +47349,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.622178375720978</v>
+        <v>0.622178316116333</v>
       </c>
       <c r="H1620" t="n">
         <v>3009</v>
@@ -47407,7 +47407,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.625654220581055</v>
+        <v>0.62565416097641</v>
       </c>
       <c r="H1622" t="n">
         <v>15124</v>
@@ -47523,7 +47523,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.613488733768463</v>
+        <v>0.613488674163818</v>
       </c>
       <c r="H1626" t="n">
         <v>49603</v>
@@ -47581,7 +47581,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.625654220581055</v>
+        <v>0.62565416097641</v>
       </c>
       <c r="H1628" t="n">
         <v>49286</v>
@@ -47610,7 +47610,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.625654220581055</v>
+        <v>0.62565416097641</v>
       </c>
       <c r="H1629" t="n">
         <v>101713</v>
@@ -80052,7 +80052,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="D2748" t="n">
-        <v>0.751999974250793</v>
+        <v>0.754000008106232</v>
       </c>
       <c r="E2748" t="n">
         <v>0.734000027179718</v>
@@ -80067,6 +80067,35 @@
         <v>1367</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.754000008106232</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.759999990463257</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.741999983787537</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.758000016212463</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>9215</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
